--- a/minio-report-tracker/xlxs/released.xlsx
+++ b/minio-report-tracker/xlxs/released.xlsx
@@ -506,31 +506,6 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>330</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="7620000" cy="3810000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="16" name="Image 16" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId16"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -823,28 +798,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI17"/>
+  <dimension ref="A1:AI16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="4" customWidth="1" min="6" max="6"/>
-    <col width="4" customWidth="1" min="7" max="7"/>
-    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="6" customWidth="1" min="12" max="12"/>
     <col width="6" customWidth="1" min="13" max="13"/>
-    <col width="4" customWidth="1" min="14" max="14"/>
+    <col width="3" customWidth="1" min="14" max="14"/>
     <col width="4" customWidth="1" min="15" max="15"/>
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
     <col width="2" customWidth="1" min="18" max="18"/>
-    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
     <col width="16" customWidth="1" min="20" max="20"/>
     <col width="6" customWidth="1" min="21" max="21"/>
     <col width="6" customWidth="1" min="22" max="22"/>
@@ -853,8 +828,8 @@
     <col width="5" customWidth="1" min="25" max="25"/>
     <col width="5" customWidth="1" min="26" max="26"/>
     <col width="2" customWidth="1" min="27" max="27"/>
-    <col width="18" customWidth="1" min="28" max="28"/>
-    <col width="12" customWidth="1" min="29" max="29"/>
+    <col width="15" customWidth="1" min="28" max="28"/>
+    <col width="16" customWidth="1" min="29" max="29"/>
     <col width="5" customWidth="1" min="30" max="30"/>
     <col width="5" customWidth="1" min="31" max="31"/>
     <col width="5" customWidth="1" min="32" max="32"/>
@@ -1028,7 +1003,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>12-December-2025</t>
+          <t>27-March-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1043,7 +1018,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>598</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1053,102 +1028,102 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>26-March-2026</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>11-December-2025</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>25-March-2026</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>535</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>10-December-2025</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>316</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09-December-2025</t>
+          <t>24-March-2026</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1158,12 +1133,12 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1190,7 +1165,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>12-December-2025</t>
+          <t>27-March-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1205,7 +1180,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>336</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1225,12 +1200,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>11-December-2025</t>
+          <t>26-March-2026</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1245,7 +1220,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>336</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1265,27 +1240,27 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>10-December-2025</t>
+          <t>25-March-2026</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>injiverify</t>
+          <t>idrepo</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>414</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>336</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1300,7 +1275,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>78</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -1310,22 +1285,22 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09-December-2025</t>
+          <t>24-March-2026</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>adminui</t>
+          <t>masterdata-ara</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>945</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>929</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1335,12 +1310,12 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1352,7 +1327,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>12-December-2025</t>
+          <t>27-March-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1362,12 +1337,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>53</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>53</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1392,7 +1367,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>11-December-2025</t>
+          <t>26-March-2026</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1402,12 +1377,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>53</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>53</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1432,72 +1407,72 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>10-December-2025</t>
+          <t>25-March-2026</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>masterdata-ara</t>
+          <t>injiverify</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>24-March-2026</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>896</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>09-December-2025</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>pmpui</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>943</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
@@ -1514,7 +1489,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>12-December-2025</t>
+          <t>27-March-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1529,7 +1504,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>929</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1539,7 +1514,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1549,12 +1524,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>11-December-2025</t>
+          <t>26-March-2026</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1569,7 +1544,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>929</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1579,7 +1554,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1589,17 +1564,17 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>10-December-2025</t>
+          <t>25-March-2026</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>masterdata-eng</t>
+          <t>masterdata-ara</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1609,7 +1584,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>929</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1619,48 +1594,64 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AB5" t="n">
-        <v/>
-      </c>
-      <c r="AC5" t="n">
-        <v/>
-      </c>
-      <c r="AD5" t="n">
-        <v/>
-      </c>
-      <c r="AE5" t="n">
-        <v/>
-      </c>
-      <c r="AF5" t="n">
-        <v/>
-      </c>
-      <c r="AG5" t="n">
-        <v/>
-      </c>
-      <c r="AH5" t="n">
-        <v/>
-      </c>
-      <c r="AI5" t="n">
-        <v/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>24-March-2026</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>12-December-2025</t>
+          <t>27-March-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1675,7 +1666,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>940</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1685,7 +1676,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1695,12 +1686,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>11-December-2025</t>
+          <t>26-March-2026</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1715,7 +1706,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>944</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1725,7 +1716,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1735,17 +1726,17 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>10-December-2025</t>
+          <t>25-March-2026</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>masterdata-fra</t>
+          <t>masterdata-eng</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1755,7 +1746,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>907</t>
+          <t>944</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1765,48 +1756,64 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>24-March-2026</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>masterdata-hin</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v/>
-      </c>
-      <c r="AC6" t="n">
-        <v/>
-      </c>
-      <c r="AD6" t="n">
-        <v/>
-      </c>
-      <c r="AE6" t="n">
-        <v/>
-      </c>
-      <c r="AF6" t="n">
-        <v/>
-      </c>
-      <c r="AG6" t="n">
-        <v/>
-      </c>
-      <c r="AH6" t="n">
-        <v/>
-      </c>
-      <c r="AI6" t="n">
-        <v/>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>12-December-2025</t>
+          <t>27-March-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1821,7 +1828,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>907</t>
+          <t>929</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1831,7 +1838,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1841,12 +1848,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>11-December-2025</t>
+          <t>26-March-2026</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1861,7 +1868,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>907</t>
+          <t>929</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1871,7 +1878,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1881,17 +1888,17 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>10-December-2025</t>
+          <t>25-March-2026</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>masterdata-hin</t>
+          <t>masterdata-fra</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1901,7 +1908,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>929</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1911,7 +1918,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1921,38 +1928,54 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v/>
-      </c>
-      <c r="AC7" t="n">
-        <v/>
-      </c>
-      <c r="AD7" t="n">
-        <v/>
-      </c>
-      <c r="AE7" t="n">
-        <v/>
-      </c>
-      <c r="AF7" t="n">
-        <v/>
-      </c>
-      <c r="AG7" t="n">
-        <v/>
-      </c>
-      <c r="AH7" t="n">
-        <v/>
-      </c>
-      <c r="AI7" t="n">
-        <v/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>24-March-2026</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>masterdata-kan</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>12-December-2025</t>
+          <t>27-March-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1967,7 +1990,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>929</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1977,7 +2000,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1987,12 +2010,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>11-December-2025</t>
+          <t>26-March-2026</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -2007,7 +2030,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>929</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -2017,7 +2040,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -2027,17 +2050,17 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>10-December-2025</t>
+          <t>25-March-2026</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>masterdata-kan</t>
+          <t>masterdata-hin</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -2047,7 +2070,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>929</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -2057,7 +2080,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -2067,38 +2090,54 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="AB8" t="n">
-        <v/>
-      </c>
-      <c r="AC8" t="n">
-        <v/>
-      </c>
-      <c r="AD8" t="n">
-        <v/>
-      </c>
-      <c r="AE8" t="n">
-        <v/>
-      </c>
-      <c r="AF8" t="n">
-        <v/>
-      </c>
-      <c r="AG8" t="n">
-        <v/>
-      </c>
-      <c r="AH8" t="n">
-        <v/>
-      </c>
-      <c r="AI8" t="n">
-        <v/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>24-March-2026</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>masterdata-tam</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>12-December-2025</t>
+          <t>27-March-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2113,7 +2152,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>929</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -2123,7 +2162,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -2133,12 +2172,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>11-December-2025</t>
+          <t>26-March-2026</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -2153,7 +2192,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>929</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -2163,7 +2202,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -2173,17 +2212,17 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>10-December-2025</t>
+          <t>25-March-2026</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>masterdata-tam</t>
+          <t>masterdata-kan</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -2193,7 +2232,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>929</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -2203,7 +2242,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -2213,38 +2252,54 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="AB9" t="n">
-        <v/>
-      </c>
-      <c r="AC9" t="n">
-        <v/>
-      </c>
-      <c r="AD9" t="n">
-        <v/>
-      </c>
-      <c r="AE9" t="n">
-        <v/>
-      </c>
-      <c r="AF9" t="n">
-        <v/>
-      </c>
-      <c r="AG9" t="n">
-        <v/>
-      </c>
-      <c r="AH9" t="n">
-        <v/>
-      </c>
-      <c r="AI9" t="n">
-        <v/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>24-March-2026</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>12-December-2025</t>
+          <t>27-March-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2259,7 +2314,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>929</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -2269,7 +2324,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -2279,12 +2334,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>11-December-2025</t>
+          <t>26-March-2026</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -2299,7 +2354,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>929</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -2309,7 +2364,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -2319,27 +2374,27 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>10-December-2025</t>
+          <t>25-March-2026</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>mimoto</t>
+          <t>masterdata-tam</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>945</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>929</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -2349,48 +2404,64 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>15</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB10" t="n">
-        <v/>
-      </c>
-      <c r="AC10" t="n">
-        <v/>
-      </c>
-      <c r="AD10" t="n">
-        <v/>
-      </c>
-      <c r="AE10" t="n">
-        <v/>
-      </c>
-      <c r="AF10" t="n">
-        <v/>
-      </c>
-      <c r="AG10" t="n">
-        <v/>
-      </c>
-      <c r="AH10" t="n">
-        <v/>
-      </c>
-      <c r="AI10" t="n">
-        <v/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>24-March-2026</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>adminui</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>12-December-2025</t>
+          <t>27-March-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2405,107 +2476,107 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>26-March-2026</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>25-March-2026</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
           <t>312</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>11-December-2025</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>mimoto</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>349</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>312</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>10-December-2025</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>495</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="AB11" t="n">
@@ -2536,7 +2607,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>12-December-2025</t>
+          <t>27-March-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2546,27 +2617,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>511</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>499</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -2576,7 +2647,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>11-December-2025</t>
+          <t>26-March-2026</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -2586,12 +2657,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>511</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>499</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2601,12 +2672,12 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -2616,22 +2687,22 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>10-December-2025</t>
+          <t>25-March-2026</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>prereg</t>
+          <t>partner</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>511</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>499</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -2646,12 +2717,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AB12" t="n">
@@ -2682,7 +2753,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>12-December-2025</t>
+          <t>27-March-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2697,7 +2768,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>282</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -2717,12 +2788,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>11-December-2025</t>
+          <t>26-March-2026</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -2737,7 +2808,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>282</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2757,27 +2828,27 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>10-December-2025</t>
+          <t>25-March-2026</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>resident</t>
+          <t>prereg</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>1142</t>
+          <t>288</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>1128</t>
+          <t>282</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -2787,17 +2858,17 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB13" t="n">
@@ -2828,7 +2899,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>12-December-2025</t>
+          <t>27-March-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2843,12 +2914,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1122</t>
+          <t>1112</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2863,12 +2934,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>11-December-2025</t>
+          <t>26-March-2026</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2883,17 +2954,17 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1128</t>
+          <t>1044</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>94</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2903,27 +2974,27 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>10-December-2025</t>
+          <t>25-March-2026</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>dsl</t>
+          <t>resident</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>1142</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>1139</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -2933,17 +3004,17 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB14" t="n">
@@ -2974,62 +3045,62 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>12-December-2025</t>
+          <t>27-March-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>adminui</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>26-March-2026</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>11-December-2025</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>209</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>178</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -3039,22 +3110,22 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>10-December-2025</t>
+          <t>25-March-2026</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
@@ -3118,61 +3189,45 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>12-December-2025</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
+      <c r="A16" t="n">
+        <v/>
+      </c>
+      <c r="B16" t="n">
+        <v/>
+      </c>
+      <c r="C16" t="n">
+        <v/>
+      </c>
+      <c r="D16" t="n">
+        <v/>
+      </c>
+      <c r="E16" t="n">
+        <v/>
+      </c>
+      <c r="F16" t="n">
+        <v/>
+      </c>
+      <c r="G16" t="n">
+        <v/>
+      </c>
+      <c r="H16" t="n">
+        <v/>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>26-March-2026</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>adminui</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>11-December-2025</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>adminui</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="M16" t="inlineStr">
         <is>
           <t>15</t>
@@ -3198,45 +3253,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>10-December-2025</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>pmpui</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="S16" t="n">
+        <v/>
+      </c>
+      <c r="T16" t="n">
+        <v/>
+      </c>
+      <c r="U16" t="n">
+        <v/>
+      </c>
+      <c r="V16" t="n">
+        <v/>
+      </c>
+      <c r="W16" t="n">
+        <v/>
+      </c>
+      <c r="X16" t="n">
+        <v/>
+      </c>
+      <c r="Y16" t="n">
+        <v/>
+      </c>
+      <c r="Z16" t="n">
+        <v/>
       </c>
       <c r="AB16" t="n">
         <v/>
@@ -3260,136 +3299,6 @@
         <v/>
       </c>
       <c r="AI16" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>12-December-2025</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>pmpui</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>11-December-2025</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>pmpui</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S17" t="n">
-        <v/>
-      </c>
-      <c r="T17" t="n">
-        <v/>
-      </c>
-      <c r="U17" t="n">
-        <v/>
-      </c>
-      <c r="V17" t="n">
-        <v/>
-      </c>
-      <c r="W17" t="n">
-        <v/>
-      </c>
-      <c r="X17" t="n">
-        <v/>
-      </c>
-      <c r="Y17" t="n">
-        <v/>
-      </c>
-      <c r="Z17" t="n">
-        <v/>
-      </c>
-      <c r="AB17" t="n">
-        <v/>
-      </c>
-      <c r="AC17" t="n">
-        <v/>
-      </c>
-      <c r="AD17" t="n">
-        <v/>
-      </c>
-      <c r="AE17" t="n">
-        <v/>
-      </c>
-      <c r="AF17" t="n">
-        <v/>
-      </c>
-      <c r="AG17" t="n">
-        <v/>
-      </c>
-      <c r="AH17" t="n">
-        <v/>
-      </c>
-      <c r="AI17" t="n">
         <v/>
       </c>
     </row>

--- a/minio-report-tracker/xlxs/released.xlsx
+++ b/minio-report-tracker/xlxs/released.xlsx
@@ -805,19 +805,19 @@
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="4" customWidth="1" min="5" max="5"/>
-    <col width="3" customWidth="1" min="6" max="6"/>
+    <col width="3" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
     <col width="4" customWidth="1" min="7" max="7"/>
     <col width="4" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
-    <col width="5" customWidth="1" min="12" max="12"/>
-    <col width="5" customWidth="1" min="13" max="13"/>
-    <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="5" customWidth="1" min="15" max="15"/>
-    <col width="5" customWidth="1" min="16" max="16"/>
-    <col width="5" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
+    <col width="4" customWidth="1" min="14" max="14"/>
+    <col width="3" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -905,1007 +905,1231 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>31-March-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>27-March-2026</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adminui</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>31-March-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v/>
-      </c>
-      <c r="K3" t="n">
-        <v/>
-      </c>
-      <c r="L3" t="n">
-        <v/>
-      </c>
-      <c r="M3" t="n">
-        <v/>
-      </c>
-      <c r="N3" t="n">
-        <v/>
-      </c>
-      <c r="O3" t="n">
-        <v/>
-      </c>
-      <c r="P3" t="n">
-        <v/>
-      </c>
-      <c r="Q3" t="n">
-        <v/>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>31-March-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v/>
-      </c>
-      <c r="K4" t="n">
-        <v/>
-      </c>
-      <c r="L4" t="n">
-        <v/>
-      </c>
-      <c r="M4" t="n">
-        <v/>
-      </c>
-      <c r="N4" t="n">
-        <v/>
-      </c>
-      <c r="O4" t="n">
-        <v/>
-      </c>
-      <c r="P4" t="n">
-        <v/>
-      </c>
-      <c r="Q4" t="n">
-        <v/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>31-March-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>928</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v/>
-      </c>
-      <c r="K5" t="n">
-        <v/>
-      </c>
-      <c r="L5" t="n">
-        <v/>
-      </c>
-      <c r="M5" t="n">
-        <v/>
-      </c>
-      <c r="N5" t="n">
-        <v/>
-      </c>
-      <c r="O5" t="n">
-        <v/>
-      </c>
-      <c r="P5" t="n">
-        <v/>
-      </c>
-      <c r="Q5" t="n">
-        <v/>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>31-March-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>940</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v/>
-      </c>
-      <c r="K6" t="n">
-        <v/>
-      </c>
-      <c r="L6" t="n">
-        <v/>
-      </c>
-      <c r="M6" t="n">
-        <v/>
-      </c>
-      <c r="N6" t="n">
-        <v/>
-      </c>
-      <c r="O6" t="n">
-        <v/>
-      </c>
-      <c r="P6" t="n">
-        <v/>
-      </c>
-      <c r="Q6" t="n">
-        <v/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>31-March-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v/>
-      </c>
-      <c r="K7" t="n">
-        <v/>
-      </c>
-      <c r="L7" t="n">
-        <v/>
-      </c>
-      <c r="M7" t="n">
-        <v/>
-      </c>
-      <c r="N7" t="n">
-        <v/>
-      </c>
-      <c r="O7" t="n">
-        <v/>
-      </c>
-      <c r="P7" t="n">
-        <v/>
-      </c>
-      <c r="Q7" t="n">
-        <v/>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>31-March-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>masterdata-hin</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>masterdata-hin</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v/>
-      </c>
-      <c r="K8" t="n">
-        <v/>
-      </c>
-      <c r="L8" t="n">
-        <v/>
-      </c>
-      <c r="M8" t="n">
-        <v/>
-      </c>
-      <c r="N8" t="n">
-        <v/>
-      </c>
-      <c r="O8" t="n">
-        <v/>
-      </c>
-      <c r="P8" t="n">
-        <v/>
-      </c>
-      <c r="Q8" t="n">
-        <v/>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>31-March-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>masterdata-kan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>masterdata-kan</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>928</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v/>
-      </c>
-      <c r="K9" t="n">
-        <v/>
-      </c>
-      <c r="L9" t="n">
-        <v/>
-      </c>
-      <c r="M9" t="n">
-        <v/>
-      </c>
-      <c r="N9" t="n">
-        <v/>
-      </c>
-      <c r="O9" t="n">
-        <v/>
-      </c>
-      <c r="P9" t="n">
-        <v/>
-      </c>
-      <c r="Q9" t="n">
-        <v/>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>31-March-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>masterdata-tam</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>masterdata-tam</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v/>
-      </c>
-      <c r="K10" t="n">
-        <v/>
-      </c>
-      <c r="L10" t="n">
-        <v/>
-      </c>
-      <c r="M10" t="n">
-        <v/>
-      </c>
-      <c r="N10" t="n">
-        <v/>
-      </c>
-      <c r="O10" t="n">
-        <v/>
-      </c>
-      <c r="P10" t="n">
-        <v/>
-      </c>
-      <c r="Q10" t="n">
-        <v/>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>31-March-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>292</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
-      </c>
-      <c r="J11" t="n">
-        <v/>
-      </c>
-      <c r="K11" t="n">
-        <v/>
-      </c>
-      <c r="L11" t="n">
-        <v/>
-      </c>
-      <c r="M11" t="n">
-        <v/>
-      </c>
-      <c r="N11" t="n">
-        <v/>
-      </c>
-      <c r="O11" t="n">
-        <v/>
-      </c>
-      <c r="P11" t="n">
-        <v/>
-      </c>
-      <c r="Q11" t="n">
-        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>31-March-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>499</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
-      </c>
-      <c r="J12" t="n">
-        <v/>
-      </c>
-      <c r="K12" t="n">
-        <v/>
-      </c>
-      <c r="L12" t="n">
-        <v/>
-      </c>
-      <c r="M12" t="n">
-        <v/>
-      </c>
-      <c r="N12" t="n">
-        <v/>
-      </c>
-      <c r="O12" t="n">
-        <v/>
-      </c>
-      <c r="P12" t="n">
-        <v/>
-      </c>
-      <c r="Q12" t="n">
-        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>31-March-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
-      </c>
-      <c r="J13" t="n">
-        <v/>
-      </c>
-      <c r="K13" t="n">
-        <v/>
-      </c>
-      <c r="L13" t="n">
-        <v/>
-      </c>
-      <c r="M13" t="n">
-        <v/>
-      </c>
-      <c r="N13" t="n">
-        <v/>
-      </c>
-      <c r="O13" t="n">
-        <v/>
-      </c>
-      <c r="P13" t="n">
-        <v/>
-      </c>
-      <c r="Q13" t="n">
-        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>31-March-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1140</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>1140</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v/>
-      </c>
-      <c r="K14" t="n">
-        <v/>
-      </c>
-      <c r="L14" t="n">
-        <v/>
-      </c>
-      <c r="M14" t="n">
-        <v/>
-      </c>
-      <c r="N14" t="n">
-        <v/>
-      </c>
-      <c r="O14" t="n">
-        <v/>
-      </c>
-      <c r="P14" t="n">
-        <v/>
-      </c>
-      <c r="Q14" t="n">
-        <v/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>31-March-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>179</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>30</t>
         </is>
-      </c>
-      <c r="J15" t="n">
-        <v/>
-      </c>
-      <c r="K15" t="n">
-        <v/>
-      </c>
-      <c r="L15" t="n">
-        <v/>
-      </c>
-      <c r="M15" t="n">
-        <v/>
-      </c>
-      <c r="N15" t="n">
-        <v/>
-      </c>
-      <c r="O15" t="n">
-        <v/>
-      </c>
-      <c r="P15" t="n">
-        <v/>
-      </c>
-      <c r="Q15" t="n">
-        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>31-March-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>adminui</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>adminui</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v/>
-      </c>
-      <c r="K16" t="n">
-        <v/>
-      </c>
-      <c r="L16" t="n">
-        <v/>
-      </c>
-      <c r="M16" t="n">
-        <v/>
-      </c>
-      <c r="N16" t="n">
-        <v/>
-      </c>
-      <c r="O16" t="n">
-        <v/>
-      </c>
-      <c r="P16" t="n">
-        <v/>
-      </c>
-      <c r="Q16" t="n">
-        <v/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/released.xlsx
+++ b/minio-report-tracker/xlxs/released.xlsx
@@ -798,26 +798,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:Z16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="3" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
     <col width="5" customWidth="1" min="6" max="6"/>
-    <col width="4" customWidth="1" min="7" max="7"/>
-    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="6" customWidth="1" min="12" max="12"/>
     <col width="6" customWidth="1" min="13" max="13"/>
-    <col width="4" customWidth="1" min="14" max="14"/>
-    <col width="3" customWidth="1" min="15" max="15"/>
+    <col width="3" customWidth="1" min="14" max="14"/>
+    <col width="5" customWidth="1" min="15" max="15"/>
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="2" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
+    <col width="4" customWidth="1" min="23" max="23"/>
+    <col width="3" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -901,84 +910,164 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>596</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -987,80 +1076,120 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1069,80 +1198,120 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1151,80 +1320,120 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>928</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1233,80 +1442,120 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>940</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>940</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1315,80 +1564,120 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1397,80 +1686,120 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>masterdata-hin</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>masterdata-hin</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>masterdata-hin</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1479,80 +1808,120 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>masterdata-kan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>masterdata-kan</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>masterdata-kan</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>928</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1561,80 +1930,120 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>masterdata-tam</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>masterdata-tam</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>masterdata-tam</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1643,80 +2052,120 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>292</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1725,80 +2174,120 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>499</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>499</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -1807,80 +2296,120 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1889,80 +2418,120 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1140</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>1140</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>1140</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1971,162 +2540,226 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>adminui</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>179</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" t="n">
+        <v/>
+      </c>
+      <c r="B16" t="n">
+        <v/>
+      </c>
+      <c r="C16" t="n">
+        <v/>
+      </c>
+      <c r="D16" t="n">
+        <v/>
+      </c>
+      <c r="E16" t="n">
+        <v/>
+      </c>
+      <c r="F16" t="n">
+        <v/>
+      </c>
+      <c r="G16" t="n">
+        <v/>
+      </c>
+      <c r="H16" t="n">
+        <v/>
+      </c>
+      <c r="J16" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>adminui</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>adminui</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/minio-report-tracker/xlxs/released.xlsx
+++ b/minio-report-tracker/xlxs/released.xlsx
@@ -798,24 +798,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z16"/>
+  <dimension ref="A1:AI16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
-    <col width="5" customWidth="1" min="7" max="7"/>
-    <col width="5" customWidth="1" min="8" max="8"/>
+    <col width="3" customWidth="1" min="5" max="5"/>
+    <col width="3" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="6" customWidth="1" min="12" max="12"/>
     <col width="6" customWidth="1" min="13" max="13"/>
     <col width="3" customWidth="1" min="14" max="14"/>
-    <col width="5" customWidth="1" min="15" max="15"/>
+    <col width="3" customWidth="1" min="15" max="15"/>
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
     <col width="2" customWidth="1" min="18" max="18"/>
@@ -823,10 +823,19 @@
     <col width="16" customWidth="1" min="20" max="20"/>
     <col width="6" customWidth="1" min="21" max="21"/>
     <col width="6" customWidth="1" min="22" max="22"/>
-    <col width="4" customWidth="1" min="23" max="23"/>
-    <col width="3" customWidth="1" min="24" max="24"/>
+    <col width="3" customWidth="1" min="23" max="23"/>
+    <col width="5" customWidth="1" min="24" max="24"/>
     <col width="4" customWidth="1" min="25" max="25"/>
     <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="2" customWidth="1" min="27" max="27"/>
+    <col width="15" customWidth="1" min="28" max="28"/>
+    <col width="9" customWidth="1" min="29" max="29"/>
+    <col width="5" customWidth="1" min="30" max="30"/>
+    <col width="5" customWidth="1" min="31" max="31"/>
+    <col width="5" customWidth="1" min="32" max="32"/>
+    <col width="5" customWidth="1" min="33" max="33"/>
+    <col width="5" customWidth="1" min="34" max="34"/>
+    <col width="5" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -950,368 +959,528 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>596</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>597</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>9</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>293</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>49</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>injiverify</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>adminui</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1320,236 +1489,260 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>928</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="Z5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB5" t="n">
+        <v/>
+      </c>
+      <c r="AC5" t="n">
+        <v/>
+      </c>
+      <c r="AD5" t="n">
+        <v/>
+      </c>
+      <c r="AE5" t="n">
+        <v/>
+      </c>
+      <c r="AF5" t="n">
+        <v/>
+      </c>
+      <c r="AG5" t="n">
+        <v/>
+      </c>
+      <c r="AH5" t="n">
+        <v/>
+      </c>
+      <c r="AI5" t="n">
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>940</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>940</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="Y6" t="inlineStr">
         <is>
           <t>0</t>
@@ -1559,973 +1752,1165 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB6" t="n">
+        <v/>
+      </c>
+      <c r="AC6" t="n">
+        <v/>
+      </c>
+      <c r="AD6" t="n">
+        <v/>
+      </c>
+      <c r="AE6" t="n">
+        <v/>
+      </c>
+      <c r="AF6" t="n">
+        <v/>
+      </c>
+      <c r="AG6" t="n">
+        <v/>
+      </c>
+      <c r="AH6" t="n">
+        <v/>
+      </c>
+      <c r="AI6" t="n">
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="Z7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB7" t="n">
+        <v/>
+      </c>
+      <c r="AC7" t="n">
+        <v/>
+      </c>
+      <c r="AD7" t="n">
+        <v/>
+      </c>
+      <c r="AE7" t="n">
+        <v/>
+      </c>
+      <c r="AF7" t="n">
+        <v/>
+      </c>
+      <c r="AG7" t="n">
+        <v/>
+      </c>
+      <c r="AH7" t="n">
+        <v/>
+      </c>
+      <c r="AI7" t="n">
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>masterdata-hin</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>masterdata-hin</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>masterdata-hin</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>masterdata-hin</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="Z8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB8" t="n">
+        <v/>
+      </c>
+      <c r="AC8" t="n">
+        <v/>
+      </c>
+      <c r="AD8" t="n">
+        <v/>
+      </c>
+      <c r="AE8" t="n">
+        <v/>
+      </c>
+      <c r="AF8" t="n">
+        <v/>
+      </c>
+      <c r="AG8" t="n">
+        <v/>
+      </c>
+      <c r="AH8" t="n">
+        <v/>
+      </c>
+      <c r="AI8" t="n">
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>masterdata-kan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>masterdata-kan</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>masterdata-kan</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>masterdata-kan</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>928</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="Z9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB9" t="n">
+        <v/>
+      </c>
+      <c r="AC9" t="n">
+        <v/>
+      </c>
+      <c r="AD9" t="n">
+        <v/>
+      </c>
+      <c r="AE9" t="n">
+        <v/>
+      </c>
+      <c r="AF9" t="n">
+        <v/>
+      </c>
+      <c r="AG9" t="n">
+        <v/>
+      </c>
+      <c r="AH9" t="n">
+        <v/>
+      </c>
+      <c r="AI9" t="n">
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>masterdata-tam</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>masterdata-tam</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>masterdata-tam</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>masterdata-tam</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="Z10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB10" t="n">
+        <v/>
+      </c>
+      <c r="AC10" t="n">
+        <v/>
+      </c>
+      <c r="AD10" t="n">
+        <v/>
+      </c>
+      <c r="AE10" t="n">
+        <v/>
+      </c>
+      <c r="AF10" t="n">
+        <v/>
+      </c>
+      <c r="AG10" t="n">
+        <v/>
+      </c>
+      <c r="AH10" t="n">
+        <v/>
+      </c>
+      <c r="AI10" t="n">
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>312</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>mimoto</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>349</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>292</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v/>
+      </c>
+      <c r="AC11" t="n">
+        <v/>
+      </c>
+      <c r="AD11" t="n">
+        <v/>
+      </c>
+      <c r="AE11" t="n">
+        <v/>
+      </c>
+      <c r="AF11" t="n">
+        <v/>
+      </c>
+      <c r="AG11" t="n">
+        <v/>
+      </c>
+      <c r="AH11" t="n">
+        <v/>
+      </c>
+      <c r="AI11" t="n">
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>499</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>499</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>499</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="AB12" t="n">
+        <v/>
+      </c>
+      <c r="AC12" t="n">
+        <v/>
+      </c>
+      <c r="AD12" t="n">
+        <v/>
+      </c>
+      <c r="AE12" t="n">
+        <v/>
+      </c>
+      <c r="AF12" t="n">
+        <v/>
+      </c>
+      <c r="AG12" t="n">
+        <v/>
+      </c>
+      <c r="AH12" t="n">
+        <v/>
+      </c>
+      <c r="AI12" t="n">
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AB13" t="n">
+        <v/>
+      </c>
+      <c r="AC13" t="n">
+        <v/>
+      </c>
+      <c r="AD13" t="n">
+        <v/>
+      </c>
+      <c r="AE13" t="n">
+        <v/>
+      </c>
+      <c r="AF13" t="n">
+        <v/>
+      </c>
+      <c r="AG13" t="n">
+        <v/>
+      </c>
+      <c r="AH13" t="n">
+        <v/>
+      </c>
+      <c r="AI13" t="n">
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1140</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>1140</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>1140</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>1140</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="Y14" t="inlineStr">
         <is>
           <t>0</t>
@@ -2535,215 +2920,279 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB14" t="n">
+        <v/>
+      </c>
+      <c r="AC14" t="n">
+        <v/>
+      </c>
+      <c r="AD14" t="n">
+        <v/>
+      </c>
+      <c r="AE14" t="n">
+        <v/>
+      </c>
+      <c r="AF14" t="n">
+        <v/>
+      </c>
+      <c r="AG14" t="n">
+        <v/>
+      </c>
+      <c r="AH14" t="n">
+        <v/>
+      </c>
+      <c r="AI14" t="n">
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>adminui</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="AB15" t="n">
+        <v/>
+      </c>
+      <c r="AC15" t="n">
+        <v/>
+      </c>
+      <c r="AD15" t="n">
+        <v/>
+      </c>
+      <c r="AE15" t="n">
+        <v/>
+      </c>
+      <c r="AF15" t="n">
+        <v/>
+      </c>
+      <c r="AG15" t="n">
+        <v/>
+      </c>
+      <c r="AH15" t="n">
+        <v/>
+      </c>
+      <c r="AI15" t="n">
+        <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v/>
-      </c>
-      <c r="B16" t="n">
-        <v/>
-      </c>
-      <c r="C16" t="n">
-        <v/>
-      </c>
-      <c r="D16" t="n">
-        <v/>
-      </c>
-      <c r="E16" t="n">
-        <v/>
-      </c>
-      <c r="F16" t="n">
-        <v/>
-      </c>
-      <c r="G16" t="n">
-        <v/>
-      </c>
-      <c r="H16" t="n">
-        <v/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>adminui</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adminui</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>adminui</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>adminui</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="W16" t="inlineStr">
         <is>
           <t>0</t>
@@ -2751,7 +3200,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2763,6 +3212,30 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB16" t="n">
+        <v/>
+      </c>
+      <c r="AC16" t="n">
+        <v/>
+      </c>
+      <c r="AD16" t="n">
+        <v/>
+      </c>
+      <c r="AE16" t="n">
+        <v/>
+      </c>
+      <c r="AF16" t="n">
+        <v/>
+      </c>
+      <c r="AG16" t="n">
+        <v/>
+      </c>
+      <c r="AH16" t="n">
+        <v/>
+      </c>
+      <c r="AI16" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/released.xlsx
+++ b/minio-report-tracker/xlxs/released.xlsx
@@ -805,8 +805,8 @@
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="3" customWidth="1" min="5" max="5"/>
-    <col width="3" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
     <col width="4" customWidth="1" min="7" max="7"/>
     <col width="4" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
@@ -824,7 +824,7 @@
     <col width="6" customWidth="1" min="21" max="21"/>
     <col width="6" customWidth="1" min="22" max="22"/>
     <col width="3" customWidth="1" min="23" max="23"/>
-    <col width="5" customWidth="1" min="24" max="24"/>
+    <col width="3" customWidth="1" min="24" max="24"/>
     <col width="4" customWidth="1" min="25" max="25"/>
     <col width="4" customWidth="1" min="26" max="26"/>
     <col width="2" customWidth="1" min="27" max="27"/>
@@ -1003,129 +1003,129 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>596</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
           <t>mimoto</t>
@@ -1138,154 +1138,154 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>349</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>31-March-2026</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1327,129 +1327,129 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>49</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>injiverify</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
           <t>adminui</t>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
@@ -1489,87 +1489,87 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>01-April-2026</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>31-March-2026</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1635,87 +1635,87 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>01-April-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>31-March-2026</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1781,87 +1781,87 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>01-April-2026</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>31-March-2026</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1927,87 +1927,87 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>masterdata-hin</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>masterdata-hin</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>01-April-2026</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>masterdata-hin</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>31-March-2026</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -2073,87 +2073,87 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>masterdata-kan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>928</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>masterdata-kan</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>01-April-2026</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>masterdata-kan</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>31-March-2026</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -2219,87 +2219,87 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>masterdata-tam</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>masterdata-tam</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>01-April-2026</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>masterdata-tam</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>31-March-2026</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -2365,122 +2365,122 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>312</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>312</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>31-March-2026</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>mimoto</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>349</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>349</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="AB11" t="n">
@@ -2511,87 +2511,87 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>499</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>01-April-2026</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>499</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>31-March-2026</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -2657,87 +2657,87 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>01-April-2026</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>31-March-2026</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
@@ -2803,87 +2803,87 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>1140</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
         <is>
           <t>01-April-2026</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>1140</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>31-March-2026</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -2949,112 +2949,112 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>179</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>178</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>31-March-2026</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>152</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -3095,112 +3095,112 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>adminui</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>adminui</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>adminui</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>31-March-2026</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>adminui</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">

--- a/minio-report-tracker/xlxs/released.xlsx
+++ b/minio-report-tracker/xlxs/released.xlsx
@@ -811,13 +811,13 @@
     <col width="4" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
-    <col width="5" customWidth="1" min="12" max="12"/>
-    <col width="5" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
     <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="5" customWidth="1" min="15" max="15"/>
-    <col width="5" customWidth="1" min="16" max="16"/>
-    <col width="5" customWidth="1" min="17" max="17"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -905,1007 +905,1231 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>596</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>03-April-2026</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adminui</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v/>
-      </c>
-      <c r="K3" t="n">
-        <v/>
-      </c>
-      <c r="L3" t="n">
-        <v/>
-      </c>
-      <c r="M3" t="n">
-        <v/>
-      </c>
-      <c r="N3" t="n">
-        <v/>
-      </c>
-      <c r="O3" t="n">
-        <v/>
-      </c>
-      <c r="P3" t="n">
-        <v/>
-      </c>
-      <c r="Q3" t="n">
-        <v/>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v/>
-      </c>
-      <c r="K4" t="n">
-        <v/>
-      </c>
-      <c r="L4" t="n">
-        <v/>
-      </c>
-      <c r="M4" t="n">
-        <v/>
-      </c>
-      <c r="N4" t="n">
-        <v/>
-      </c>
-      <c r="O4" t="n">
-        <v/>
-      </c>
-      <c r="P4" t="n">
-        <v/>
-      </c>
-      <c r="Q4" t="n">
-        <v/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v/>
-      </c>
-      <c r="K5" t="n">
-        <v/>
-      </c>
-      <c r="L5" t="n">
-        <v/>
-      </c>
-      <c r="M5" t="n">
-        <v/>
-      </c>
-      <c r="N5" t="n">
-        <v/>
-      </c>
-      <c r="O5" t="n">
-        <v/>
-      </c>
-      <c r="P5" t="n">
-        <v/>
-      </c>
-      <c r="Q5" t="n">
-        <v/>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v/>
-      </c>
-      <c r="K6" t="n">
-        <v/>
-      </c>
-      <c r="L6" t="n">
-        <v/>
-      </c>
-      <c r="M6" t="n">
-        <v/>
-      </c>
-      <c r="N6" t="n">
-        <v/>
-      </c>
-      <c r="O6" t="n">
-        <v/>
-      </c>
-      <c r="P6" t="n">
-        <v/>
-      </c>
-      <c r="Q6" t="n">
-        <v/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v/>
-      </c>
-      <c r="K7" t="n">
-        <v/>
-      </c>
-      <c r="L7" t="n">
-        <v/>
-      </c>
-      <c r="M7" t="n">
-        <v/>
-      </c>
-      <c r="N7" t="n">
-        <v/>
-      </c>
-      <c r="O7" t="n">
-        <v/>
-      </c>
-      <c r="P7" t="n">
-        <v/>
-      </c>
-      <c r="Q7" t="n">
-        <v/>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>masterdata-hin</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>masterdata-hin</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v/>
-      </c>
-      <c r="K8" t="n">
-        <v/>
-      </c>
-      <c r="L8" t="n">
-        <v/>
-      </c>
-      <c r="M8" t="n">
-        <v/>
-      </c>
-      <c r="N8" t="n">
-        <v/>
-      </c>
-      <c r="O8" t="n">
-        <v/>
-      </c>
-      <c r="P8" t="n">
-        <v/>
-      </c>
-      <c r="Q8" t="n">
-        <v/>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>masterdata-kan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>masterdata-kan</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v/>
-      </c>
-      <c r="K9" t="n">
-        <v/>
-      </c>
-      <c r="L9" t="n">
-        <v/>
-      </c>
-      <c r="M9" t="n">
-        <v/>
-      </c>
-      <c r="N9" t="n">
-        <v/>
-      </c>
-      <c r="O9" t="n">
-        <v/>
-      </c>
-      <c r="P9" t="n">
-        <v/>
-      </c>
-      <c r="Q9" t="n">
-        <v/>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>masterdata-tam</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>masterdata-tam</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v/>
-      </c>
-      <c r="K10" t="n">
-        <v/>
-      </c>
-      <c r="L10" t="n">
-        <v/>
-      </c>
-      <c r="M10" t="n">
-        <v/>
-      </c>
-      <c r="N10" t="n">
-        <v/>
-      </c>
-      <c r="O10" t="n">
-        <v/>
-      </c>
-      <c r="P10" t="n">
-        <v/>
-      </c>
-      <c r="Q10" t="n">
-        <v/>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>312</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
-      </c>
-      <c r="J11" t="n">
-        <v/>
-      </c>
-      <c r="K11" t="n">
-        <v/>
-      </c>
-      <c r="L11" t="n">
-        <v/>
-      </c>
-      <c r="M11" t="n">
-        <v/>
-      </c>
-      <c r="N11" t="n">
-        <v/>
-      </c>
-      <c r="O11" t="n">
-        <v/>
-      </c>
-      <c r="P11" t="n">
-        <v/>
-      </c>
-      <c r="Q11" t="n">
-        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>342</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
-      </c>
-      <c r="J12" t="n">
-        <v/>
-      </c>
-      <c r="K12" t="n">
-        <v/>
-      </c>
-      <c r="L12" t="n">
-        <v/>
-      </c>
-      <c r="M12" t="n">
-        <v/>
-      </c>
-      <c r="N12" t="n">
-        <v/>
-      </c>
-      <c r="O12" t="n">
-        <v/>
-      </c>
-      <c r="P12" t="n">
-        <v/>
-      </c>
-      <c r="Q12" t="n">
-        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
-      </c>
-      <c r="J13" t="n">
-        <v/>
-      </c>
-      <c r="K13" t="n">
-        <v/>
-      </c>
-      <c r="L13" t="n">
-        <v/>
-      </c>
-      <c r="M13" t="n">
-        <v/>
-      </c>
-      <c r="N13" t="n">
-        <v/>
-      </c>
-      <c r="O13" t="n">
-        <v/>
-      </c>
-      <c r="P13" t="n">
-        <v/>
-      </c>
-      <c r="Q13" t="n">
-        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v/>
-      </c>
-      <c r="K14" t="n">
-        <v/>
-      </c>
-      <c r="L14" t="n">
-        <v/>
-      </c>
-      <c r="M14" t="n">
-        <v/>
-      </c>
-      <c r="N14" t="n">
-        <v/>
-      </c>
-      <c r="O14" t="n">
-        <v/>
-      </c>
-      <c r="P14" t="n">
-        <v/>
-      </c>
-      <c r="Q14" t="n">
-        <v/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>176</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>30</t>
         </is>
-      </c>
-      <c r="J15" t="n">
-        <v/>
-      </c>
-      <c r="K15" t="n">
-        <v/>
-      </c>
-      <c r="L15" t="n">
-        <v/>
-      </c>
-      <c r="M15" t="n">
-        <v/>
-      </c>
-      <c r="N15" t="n">
-        <v/>
-      </c>
-      <c r="O15" t="n">
-        <v/>
-      </c>
-      <c r="P15" t="n">
-        <v/>
-      </c>
-      <c r="Q15" t="n">
-        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>adminui</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>adminui</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v/>
-      </c>
-      <c r="K16" t="n">
-        <v/>
-      </c>
-      <c r="L16" t="n">
-        <v/>
-      </c>
-      <c r="M16" t="n">
-        <v/>
-      </c>
-      <c r="N16" t="n">
-        <v/>
-      </c>
-      <c r="O16" t="n">
-        <v/>
-      </c>
-      <c r="P16" t="n">
-        <v/>
-      </c>
-      <c r="Q16" t="n">
-        <v/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/released.xlsx
+++ b/minio-report-tracker/xlxs/released.xlsx
@@ -798,7 +798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:Z16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -818,6 +818,15 @@
     <col width="4" customWidth="1" min="15" max="15"/>
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="2" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
+    <col width="5" customWidth="1" min="23" max="23"/>
+    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -901,84 +910,164 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>596</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -987,80 +1076,120 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1069,80 +1198,120 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1151,80 +1320,120 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1233,80 +1442,120 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1315,80 +1564,120 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1397,80 +1686,120 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>masterdata-hin</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>masterdata-hin</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>masterdata-hin</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1479,80 +1808,120 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>masterdata-kan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>masterdata-kan</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>masterdata-kan</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1561,80 +1930,120 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>masterdata-tam</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>masterdata-tam</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>masterdata-tam</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1643,80 +2052,120 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>294</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>312</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1725,80 +2174,120 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>342</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -1807,80 +2296,120 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1889,80 +2418,120 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1971,80 +2540,120 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>06-April-2026</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>06-April-2026</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>176</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
         <is>
           <t>30</t>
         </is>
@@ -2053,80 +2662,120 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>adminui</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>adminui</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>adminui</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/minio-report-tracker/xlxs/released.xlsx
+++ b/minio-report-tracker/xlxs/released.xlsx
@@ -798,7 +798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z16"/>
+  <dimension ref="A1:AI16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -827,6 +827,15 @@
     <col width="4" customWidth="1" min="24" max="24"/>
     <col width="4" customWidth="1" min="25" max="25"/>
     <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="2" customWidth="1" min="27" max="27"/>
+    <col width="15" customWidth="1" min="28" max="28"/>
+    <col width="9" customWidth="1" min="29" max="29"/>
+    <col width="5" customWidth="1" min="30" max="30"/>
+    <col width="5" customWidth="1" min="31" max="31"/>
+    <col width="5" customWidth="1" min="32" max="32"/>
+    <col width="5" customWidth="1" min="33" max="33"/>
+    <col width="5" customWidth="1" min="34" max="34"/>
+    <col width="5" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -950,246 +959,366 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>596</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>9</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>adminui</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1198,114 +1327,114 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>06-April-2026</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>injiverify</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="Y4" t="inlineStr">
         <is>
           <t>0</t>
@@ -1315,241 +1444,289 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB4" t="n">
+        <v/>
+      </c>
+      <c r="AC4" t="n">
+        <v/>
+      </c>
+      <c r="AD4" t="n">
+        <v/>
+      </c>
+      <c r="AE4" t="n">
+        <v/>
+      </c>
+      <c r="AF4" t="n">
+        <v/>
+      </c>
+      <c r="AG4" t="n">
+        <v/>
+      </c>
+      <c r="AH4" t="n">
+        <v/>
+      </c>
+      <c r="AI4" t="n">
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>06-April-2026</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="Z5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB5" t="n">
+        <v/>
+      </c>
+      <c r="AC5" t="n">
+        <v/>
+      </c>
+      <c r="AD5" t="n">
+        <v/>
+      </c>
+      <c r="AE5" t="n">
+        <v/>
+      </c>
+      <c r="AF5" t="n">
+        <v/>
+      </c>
+      <c r="AG5" t="n">
+        <v/>
+      </c>
+      <c r="AH5" t="n">
+        <v/>
+      </c>
+      <c r="AI5" t="n">
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>06-April-2026</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="Y6" t="inlineStr">
         <is>
           <t>0</t>
@@ -1559,973 +1736,1165 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB6" t="n">
+        <v/>
+      </c>
+      <c r="AC6" t="n">
+        <v/>
+      </c>
+      <c r="AD6" t="n">
+        <v/>
+      </c>
+      <c r="AE6" t="n">
+        <v/>
+      </c>
+      <c r="AF6" t="n">
+        <v/>
+      </c>
+      <c r="AG6" t="n">
+        <v/>
+      </c>
+      <c r="AH6" t="n">
+        <v/>
+      </c>
+      <c r="AI6" t="n">
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>06-April-2026</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="Z7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB7" t="n">
+        <v/>
+      </c>
+      <c r="AC7" t="n">
+        <v/>
+      </c>
+      <c r="AD7" t="n">
+        <v/>
+      </c>
+      <c r="AE7" t="n">
+        <v/>
+      </c>
+      <c r="AF7" t="n">
+        <v/>
+      </c>
+      <c r="AG7" t="n">
+        <v/>
+      </c>
+      <c r="AH7" t="n">
+        <v/>
+      </c>
+      <c r="AI7" t="n">
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>masterdata-hin</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>masterdata-hin</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>masterdata-hin</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>06-April-2026</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>masterdata-hin</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="Z8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB8" t="n">
+        <v/>
+      </c>
+      <c r="AC8" t="n">
+        <v/>
+      </c>
+      <c r="AD8" t="n">
+        <v/>
+      </c>
+      <c r="AE8" t="n">
+        <v/>
+      </c>
+      <c r="AF8" t="n">
+        <v/>
+      </c>
+      <c r="AG8" t="n">
+        <v/>
+      </c>
+      <c r="AH8" t="n">
+        <v/>
+      </c>
+      <c r="AI8" t="n">
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>masterdata-kan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>masterdata-kan</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>masterdata-kan</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>06-April-2026</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>masterdata-kan</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="Z9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB9" t="n">
+        <v/>
+      </c>
+      <c r="AC9" t="n">
+        <v/>
+      </c>
+      <c r="AD9" t="n">
+        <v/>
+      </c>
+      <c r="AE9" t="n">
+        <v/>
+      </c>
+      <c r="AF9" t="n">
+        <v/>
+      </c>
+      <c r="AG9" t="n">
+        <v/>
+      </c>
+      <c r="AH9" t="n">
+        <v/>
+      </c>
+      <c r="AI9" t="n">
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>masterdata-tam</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>masterdata-tam</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>masterdata-tam</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>06-April-2026</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>masterdata-tam</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="Z10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB10" t="n">
+        <v/>
+      </c>
+      <c r="AC10" t="n">
+        <v/>
+      </c>
+      <c r="AD10" t="n">
+        <v/>
+      </c>
+      <c r="AE10" t="n">
+        <v/>
+      </c>
+      <c r="AF10" t="n">
+        <v/>
+      </c>
+      <c r="AG10" t="n">
+        <v/>
+      </c>
+      <c r="AH10" t="n">
+        <v/>
+      </c>
+      <c r="AI10" t="n">
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>293</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>294</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>294</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>06-April-2026</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>mimoto</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>349</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>312</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AB11" t="n">
+        <v/>
+      </c>
+      <c r="AC11" t="n">
+        <v/>
+      </c>
+      <c r="AD11" t="n">
+        <v/>
+      </c>
+      <c r="AE11" t="n">
+        <v/>
+      </c>
+      <c r="AF11" t="n">
+        <v/>
+      </c>
+      <c r="AG11" t="n">
+        <v/>
+      </c>
+      <c r="AH11" t="n">
+        <v/>
+      </c>
+      <c r="AI11" t="n">
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>06-April-2026</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>342</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="AB12" t="n">
+        <v/>
+      </c>
+      <c r="AC12" t="n">
+        <v/>
+      </c>
+      <c r="AD12" t="n">
+        <v/>
+      </c>
+      <c r="AE12" t="n">
+        <v/>
+      </c>
+      <c r="AF12" t="n">
+        <v/>
+      </c>
+      <c r="AG12" t="n">
+        <v/>
+      </c>
+      <c r="AH12" t="n">
+        <v/>
+      </c>
+      <c r="AI12" t="n">
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>06-April-2026</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AB13" t="n">
+        <v/>
+      </c>
+      <c r="AC13" t="n">
+        <v/>
+      </c>
+      <c r="AD13" t="n">
+        <v/>
+      </c>
+      <c r="AE13" t="n">
+        <v/>
+      </c>
+      <c r="AF13" t="n">
+        <v/>
+      </c>
+      <c r="AG13" t="n">
+        <v/>
+      </c>
+      <c r="AH13" t="n">
+        <v/>
+      </c>
+      <c r="AI13" t="n">
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1140</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>06-April-2026</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>1141</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="Y14" t="inlineStr">
         <is>
           <t>0</t>
@@ -2535,119 +2904,143 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB14" t="n">
+        <v/>
+      </c>
+      <c r="AC14" t="n">
+        <v/>
+      </c>
+      <c r="AD14" t="n">
+        <v/>
+      </c>
+      <c r="AE14" t="n">
+        <v/>
+      </c>
+      <c r="AF14" t="n">
+        <v/>
+      </c>
+      <c r="AG14" t="n">
+        <v/>
+      </c>
+      <c r="AH14" t="n">
+        <v/>
+      </c>
+      <c r="AI14" t="n">
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>85</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>201</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>06-April-2026</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="Y15" t="inlineStr">
         <is>
           <t>0</t>
@@ -2655,111 +3048,135 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v/>
+      </c>
+      <c r="AC15" t="n">
+        <v/>
+      </c>
+      <c r="AD15" t="n">
+        <v/>
+      </c>
+      <c r="AE15" t="n">
+        <v/>
+      </c>
+      <c r="AF15" t="n">
+        <v/>
+      </c>
+      <c r="AG15" t="n">
+        <v/>
+      </c>
+      <c r="AH15" t="n">
+        <v/>
+      </c>
+      <c r="AI15" t="n">
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>adminui</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>adminui</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>adminui</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>06-April-2026</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>adminui</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="W16" t="inlineStr">
         <is>
           <t>0</t>
@@ -2767,7 +3184,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2779,6 +3196,30 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB16" t="n">
+        <v/>
+      </c>
+      <c r="AC16" t="n">
+        <v/>
+      </c>
+      <c r="AD16" t="n">
+        <v/>
+      </c>
+      <c r="AE16" t="n">
+        <v/>
+      </c>
+      <c r="AF16" t="n">
+        <v/>
+      </c>
+      <c r="AG16" t="n">
+        <v/>
+      </c>
+      <c r="AH16" t="n">
+        <v/>
+      </c>
+      <c r="AI16" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/released.xlsx
+++ b/minio-report-tracker/xlxs/released.xlsx
@@ -1003,152 +1003,152 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>06-April-2026</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>partner</t>
+          <t>dsl</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>230</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>201</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
@@ -1158,136 +1158,136 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>06-April-2026</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
           <t>adminui</t>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
@@ -1327,87 +1327,87 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>08-April-2026</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>injiverify</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>07-April-2026</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1473,87 +1473,87 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>08-April-2026</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>07-April-2026</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1619,87 +1619,87 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>08-April-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>07-April-2026</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1765,87 +1765,87 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>08-April-2026</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>07-April-2026</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1911,87 +1911,87 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>masterdata-hin</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>masterdata-hin</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>08-April-2026</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>masterdata-hin</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>07-April-2026</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -2057,87 +2057,87 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>masterdata-kan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>masterdata-kan</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>08-April-2026</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>masterdata-kan</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>07-April-2026</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -2203,87 +2203,87 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>masterdata-tam</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>masterdata-tam</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>08-April-2026</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>masterdata-tam</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>07-April-2026</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -2349,87 +2349,87 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>293</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>08-April-2026</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>mimoto</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>349</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>294</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>07-April-2026</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -2495,87 +2495,87 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>08-April-2026</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>349</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>07-April-2026</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -2641,87 +2641,87 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>08-April-2026</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>07-April-2026</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
@@ -2787,87 +2787,87 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>1140</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
         <is>
           <t>08-April-2026</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>1141</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>07-April-2026</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -2933,112 +2933,112 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>202</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>85</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>07-April-2026</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -3079,87 +3079,87 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>adminui</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>adminui</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
         <is>
           <t>08-April-2026</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>adminui</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>07-April-2026</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">

--- a/minio-report-tracker/xlxs/released.xlsx
+++ b/minio-report-tracker/xlxs/released.xlsx
@@ -806,18 +806,18 @@
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="4" customWidth="1" min="6" max="6"/>
-    <col width="4" customWidth="1" min="7" max="7"/>
-    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
-    <col width="5" customWidth="1" min="12" max="12"/>
-    <col width="5" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
     <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="5" customWidth="1" min="15" max="15"/>
-    <col width="5" customWidth="1" min="16" max="16"/>
-    <col width="5" customWidth="1" min="17" max="17"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -905,1007 +905,1215 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>14-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>10-April-2026</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adminui</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>14-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v/>
-      </c>
-      <c r="K3" t="n">
-        <v/>
-      </c>
-      <c r="L3" t="n">
-        <v/>
-      </c>
-      <c r="M3" t="n">
-        <v/>
-      </c>
-      <c r="N3" t="n">
-        <v/>
-      </c>
-      <c r="O3" t="n">
-        <v/>
-      </c>
-      <c r="P3" t="n">
-        <v/>
-      </c>
-      <c r="Q3" t="n">
-        <v/>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>14-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v/>
-      </c>
-      <c r="K4" t="n">
-        <v/>
-      </c>
-      <c r="L4" t="n">
-        <v/>
-      </c>
-      <c r="M4" t="n">
-        <v/>
-      </c>
-      <c r="N4" t="n">
-        <v/>
-      </c>
-      <c r="O4" t="n">
-        <v/>
-      </c>
-      <c r="P4" t="n">
-        <v/>
-      </c>
-      <c r="Q4" t="n">
-        <v/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>14-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v/>
-      </c>
-      <c r="K5" t="n">
-        <v/>
-      </c>
-      <c r="L5" t="n">
-        <v/>
-      </c>
-      <c r="M5" t="n">
-        <v/>
-      </c>
-      <c r="N5" t="n">
-        <v/>
-      </c>
-      <c r="O5" t="n">
-        <v/>
-      </c>
-      <c r="P5" t="n">
-        <v/>
-      </c>
-      <c r="Q5" t="n">
-        <v/>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>14-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v/>
-      </c>
-      <c r="K6" t="n">
-        <v/>
-      </c>
-      <c r="L6" t="n">
-        <v/>
-      </c>
-      <c r="M6" t="n">
-        <v/>
-      </c>
-      <c r="N6" t="n">
-        <v/>
-      </c>
-      <c r="O6" t="n">
-        <v/>
-      </c>
-      <c r="P6" t="n">
-        <v/>
-      </c>
-      <c r="Q6" t="n">
-        <v/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>14-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v/>
-      </c>
-      <c r="K7" t="n">
-        <v/>
-      </c>
-      <c r="L7" t="n">
-        <v/>
-      </c>
-      <c r="M7" t="n">
-        <v/>
-      </c>
-      <c r="N7" t="n">
-        <v/>
-      </c>
-      <c r="O7" t="n">
-        <v/>
-      </c>
-      <c r="P7" t="n">
-        <v/>
-      </c>
-      <c r="Q7" t="n">
-        <v/>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>14-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>masterdata-hin</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>masterdata-hin</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>928</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v/>
-      </c>
-      <c r="K8" t="n">
-        <v/>
-      </c>
-      <c r="L8" t="n">
-        <v/>
-      </c>
-      <c r="M8" t="n">
-        <v/>
-      </c>
-      <c r="N8" t="n">
-        <v/>
-      </c>
-      <c r="O8" t="n">
-        <v/>
-      </c>
-      <c r="P8" t="n">
-        <v/>
-      </c>
-      <c r="Q8" t="n">
-        <v/>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>14-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>masterdata-kan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>masterdata-kan</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v/>
-      </c>
-      <c r="K9" t="n">
-        <v/>
-      </c>
-      <c r="L9" t="n">
-        <v/>
-      </c>
-      <c r="M9" t="n">
-        <v/>
-      </c>
-      <c r="N9" t="n">
-        <v/>
-      </c>
-      <c r="O9" t="n">
-        <v/>
-      </c>
-      <c r="P9" t="n">
-        <v/>
-      </c>
-      <c r="Q9" t="n">
-        <v/>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>14-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>masterdata-tam</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>masterdata-tam</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v/>
-      </c>
-      <c r="K10" t="n">
-        <v/>
-      </c>
-      <c r="L10" t="n">
-        <v/>
-      </c>
-      <c r="M10" t="n">
-        <v/>
-      </c>
-      <c r="N10" t="n">
-        <v/>
-      </c>
-      <c r="O10" t="n">
-        <v/>
-      </c>
-      <c r="P10" t="n">
-        <v/>
-      </c>
-      <c r="Q10" t="n">
-        <v/>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>14-April-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>294</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
-      </c>
-      <c r="J11" t="n">
-        <v/>
-      </c>
-      <c r="K11" t="n">
-        <v/>
-      </c>
-      <c r="L11" t="n">
-        <v/>
-      </c>
-      <c r="M11" t="n">
-        <v/>
-      </c>
-      <c r="N11" t="n">
-        <v/>
-      </c>
-      <c r="O11" t="n">
-        <v/>
-      </c>
-      <c r="P11" t="n">
-        <v/>
-      </c>
-      <c r="Q11" t="n">
-        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>14-April-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>345</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
-      </c>
-      <c r="J12" t="n">
-        <v/>
-      </c>
-      <c r="K12" t="n">
-        <v/>
-      </c>
-      <c r="L12" t="n">
-        <v/>
-      </c>
-      <c r="M12" t="n">
-        <v/>
-      </c>
-      <c r="N12" t="n">
-        <v/>
-      </c>
-      <c r="O12" t="n">
-        <v/>
-      </c>
-      <c r="P12" t="n">
-        <v/>
-      </c>
-      <c r="Q12" t="n">
-        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>14-April-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1140</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
-      </c>
-      <c r="J13" t="n">
-        <v/>
-      </c>
-      <c r="K13" t="n">
-        <v/>
-      </c>
-      <c r="L13" t="n">
-        <v/>
-      </c>
-      <c r="M13" t="n">
-        <v/>
-      </c>
-      <c r="N13" t="n">
-        <v/>
-      </c>
-      <c r="O13" t="n">
-        <v/>
-      </c>
-      <c r="P13" t="n">
-        <v/>
-      </c>
-      <c r="Q13" t="n">
-        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>14-April-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v/>
-      </c>
-      <c r="K14" t="n">
-        <v/>
-      </c>
-      <c r="L14" t="n">
-        <v/>
-      </c>
-      <c r="M14" t="n">
-        <v/>
-      </c>
-      <c r="N14" t="n">
-        <v/>
-      </c>
-      <c r="O14" t="n">
-        <v/>
-      </c>
-      <c r="P14" t="n">
-        <v/>
-      </c>
-      <c r="Q14" t="n">
-        <v/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>14-April-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>adminui</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>173</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v/>
-      </c>
-      <c r="K15" t="n">
-        <v/>
-      </c>
-      <c r="L15" t="n">
-        <v/>
-      </c>
-      <c r="M15" t="n">
-        <v/>
-      </c>
-      <c r="N15" t="n">
-        <v/>
-      </c>
-      <c r="O15" t="n">
-        <v/>
-      </c>
-      <c r="P15" t="n">
-        <v/>
-      </c>
-      <c r="Q15" t="n">
-        <v/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" t="n">
+        <v/>
+      </c>
+      <c r="B16" t="n">
+        <v/>
+      </c>
+      <c r="C16" t="n">
+        <v/>
+      </c>
+      <c r="D16" t="n">
+        <v/>
+      </c>
+      <c r="E16" t="n">
+        <v/>
+      </c>
+      <c r="F16" t="n">
+        <v/>
+      </c>
+      <c r="G16" t="n">
+        <v/>
+      </c>
+      <c r="H16" t="n">
+        <v/>
+      </c>
+      <c r="J16" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>adminui</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v/>
-      </c>
-      <c r="K16" t="n">
-        <v/>
-      </c>
-      <c r="L16" t="n">
-        <v/>
-      </c>
-      <c r="M16" t="n">
-        <v/>
-      </c>
-      <c r="N16" t="n">
-        <v/>
-      </c>
-      <c r="O16" t="n">
-        <v/>
-      </c>
-      <c r="P16" t="n">
-        <v/>
-      </c>
-      <c r="Q16" t="n">
-        <v/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/released.xlsx
+++ b/minio-report-tracker/xlxs/released.xlsx
@@ -798,7 +798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:Z16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -815,9 +815,18 @@
     <col width="6" customWidth="1" min="12" max="12"/>
     <col width="6" customWidth="1" min="13" max="13"/>
     <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="4" customWidth="1" min="15" max="15"/>
-    <col width="4" customWidth="1" min="16" max="16"/>
-    <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="5" customWidth="1" min="15" max="15"/>
+    <col width="5" customWidth="1" min="16" max="16"/>
+    <col width="5" customWidth="1" min="17" max="17"/>
+    <col width="2" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
+    <col width="5" customWidth="1" min="23" max="23"/>
+    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -901,84 +910,164 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>15-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -987,80 +1076,120 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>15-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1069,80 +1198,120 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>15-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1151,80 +1320,120 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>15-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1233,80 +1442,120 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>15-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1315,80 +1564,120 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>15-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1397,80 +1686,120 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>15-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>masterdata-hin</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>masterdata-hin</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>masterdata-hin</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>928</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1479,80 +1808,120 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>15-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>masterdata-kan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>masterdata-kan</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>masterdata-kan</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1561,80 +1930,120 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>15-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>masterdata-tam</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>928</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>masterdata-tam</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>masterdata-tam</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1643,80 +2052,120 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>15-April-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>294</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1725,80 +2174,120 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>15-April-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>345</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -1807,80 +2296,120 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>15-April-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>1140</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1889,80 +2418,120 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>15-April-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>168</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1971,80 +2540,120 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>15-April-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>adminui</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>adminui</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>173</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -2075,42 +2684,66 @@
       <c r="H16" t="n">
         <v/>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J16" t="n">
+        <v/>
+      </c>
+      <c r="K16" t="n">
+        <v/>
+      </c>
+      <c r="L16" t="n">
+        <v/>
+      </c>
+      <c r="M16" t="n">
+        <v/>
+      </c>
+      <c r="N16" t="n">
+        <v/>
+      </c>
+      <c r="O16" t="n">
+        <v/>
+      </c>
+      <c r="P16" t="n">
+        <v/>
+      </c>
+      <c r="Q16" t="n">
+        <v/>
+      </c>
+      <c r="S16" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>adminui</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/minio-report-tracker/xlxs/released.xlsx
+++ b/minio-report-tracker/xlxs/released.xlsx
@@ -798,7 +798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z16"/>
+  <dimension ref="A1:AI16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -806,27 +806,36 @@
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
-    <col width="5" customWidth="1" min="7" max="7"/>
-    <col width="5" customWidth="1" min="8" max="8"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="6" customWidth="1" min="12" max="12"/>
     <col width="6" customWidth="1" min="13" max="13"/>
     <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="5" customWidth="1" min="15" max="15"/>
-    <col width="5" customWidth="1" min="16" max="16"/>
-    <col width="5" customWidth="1" min="17" max="17"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
     <col width="2" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
     <col width="16" customWidth="1" min="20" max="20"/>
     <col width="6" customWidth="1" min="21" max="21"/>
     <col width="6" customWidth="1" min="22" max="22"/>
     <col width="5" customWidth="1" min="23" max="23"/>
-    <col width="4" customWidth="1" min="24" max="24"/>
-    <col width="4" customWidth="1" min="25" max="25"/>
-    <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="5" customWidth="1" min="24" max="24"/>
+    <col width="5" customWidth="1" min="25" max="25"/>
+    <col width="5" customWidth="1" min="26" max="26"/>
+    <col width="2" customWidth="1" min="27" max="27"/>
+    <col width="15" customWidth="1" min="28" max="28"/>
+    <col width="9" customWidth="1" min="29" max="29"/>
+    <col width="5" customWidth="1" min="30" max="30"/>
+    <col width="5" customWidth="1" min="31" max="31"/>
+    <col width="5" customWidth="1" min="32" max="32"/>
+    <col width="5" customWidth="1" min="33" max="33"/>
+    <col width="5" customWidth="1" min="34" max="34"/>
+    <col width="5" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -950,362 +959,466 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>16-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>9</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>adminui</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>16-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>13-April-2026</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
       <c r="Z3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB3" t="n">
+        <v/>
+      </c>
+      <c r="AC3" t="n">
+        <v/>
+      </c>
+      <c r="AD3" t="n">
+        <v/>
+      </c>
+      <c r="AE3" t="n">
+        <v/>
+      </c>
+      <c r="AF3" t="n">
+        <v/>
+      </c>
+      <c r="AG3" t="n">
+        <v/>
+      </c>
+      <c r="AH3" t="n">
+        <v/>
+      </c>
+      <c r="AI3" t="n">
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>16-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>13-April-2026</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>injiverify</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="Y4" t="inlineStr">
         <is>
           <t>0</t>
@@ -1315,241 +1428,289 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB4" t="n">
+        <v/>
+      </c>
+      <c r="AC4" t="n">
+        <v/>
+      </c>
+      <c r="AD4" t="n">
+        <v/>
+      </c>
+      <c r="AE4" t="n">
+        <v/>
+      </c>
+      <c r="AF4" t="n">
+        <v/>
+      </c>
+      <c r="AG4" t="n">
+        <v/>
+      </c>
+      <c r="AH4" t="n">
+        <v/>
+      </c>
+      <c r="AI4" t="n">
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>16-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>13-April-2026</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="Z5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB5" t="n">
+        <v/>
+      </c>
+      <c r="AC5" t="n">
+        <v/>
+      </c>
+      <c r="AD5" t="n">
+        <v/>
+      </c>
+      <c r="AE5" t="n">
+        <v/>
+      </c>
+      <c r="AF5" t="n">
+        <v/>
+      </c>
+      <c r="AG5" t="n">
+        <v/>
+      </c>
+      <c r="AH5" t="n">
+        <v/>
+      </c>
+      <c r="AI5" t="n">
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>16-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>943</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>13-April-2026</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="Y6" t="inlineStr">
         <is>
           <t>0</t>
@@ -1559,973 +1720,1165 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB6" t="n">
+        <v/>
+      </c>
+      <c r="AC6" t="n">
+        <v/>
+      </c>
+      <c r="AD6" t="n">
+        <v/>
+      </c>
+      <c r="AE6" t="n">
+        <v/>
+      </c>
+      <c r="AF6" t="n">
+        <v/>
+      </c>
+      <c r="AG6" t="n">
+        <v/>
+      </c>
+      <c r="AH6" t="n">
+        <v/>
+      </c>
+      <c r="AI6" t="n">
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>16-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>13-April-2026</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="Z7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB7" t="n">
+        <v/>
+      </c>
+      <c r="AC7" t="n">
+        <v/>
+      </c>
+      <c r="AD7" t="n">
+        <v/>
+      </c>
+      <c r="AE7" t="n">
+        <v/>
+      </c>
+      <c r="AF7" t="n">
+        <v/>
+      </c>
+      <c r="AG7" t="n">
+        <v/>
+      </c>
+      <c r="AH7" t="n">
+        <v/>
+      </c>
+      <c r="AI7" t="n">
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>16-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>masterdata-hin</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>masterdata-hin</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>masterdata-hin</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>13-April-2026</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>masterdata-hin</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>928</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="Z8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB8" t="n">
+        <v/>
+      </c>
+      <c r="AC8" t="n">
+        <v/>
+      </c>
+      <c r="AD8" t="n">
+        <v/>
+      </c>
+      <c r="AE8" t="n">
+        <v/>
+      </c>
+      <c r="AF8" t="n">
+        <v/>
+      </c>
+      <c r="AG8" t="n">
+        <v/>
+      </c>
+      <c r="AH8" t="n">
+        <v/>
+      </c>
+      <c r="AI8" t="n">
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>16-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>masterdata-kan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>masterdata-kan</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>masterdata-kan</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>13-April-2026</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>masterdata-kan</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="Z9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB9" t="n">
+        <v/>
+      </c>
+      <c r="AC9" t="n">
+        <v/>
+      </c>
+      <c r="AD9" t="n">
+        <v/>
+      </c>
+      <c r="AE9" t="n">
+        <v/>
+      </c>
+      <c r="AF9" t="n">
+        <v/>
+      </c>
+      <c r="AG9" t="n">
+        <v/>
+      </c>
+      <c r="AH9" t="n">
+        <v/>
+      </c>
+      <c r="AI9" t="n">
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>16-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>masterdata-tam</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>masterdata-tam</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>928</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>masterdata-tam</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>13-April-2026</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>masterdata-tam</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="Z10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB10" t="n">
+        <v/>
+      </c>
+      <c r="AC10" t="n">
+        <v/>
+      </c>
+      <c r="AD10" t="n">
+        <v/>
+      </c>
+      <c r="AE10" t="n">
+        <v/>
+      </c>
+      <c r="AF10" t="n">
+        <v/>
+      </c>
+      <c r="AG10" t="n">
+        <v/>
+      </c>
+      <c r="AH10" t="n">
+        <v/>
+      </c>
+      <c r="AI10" t="n">
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>16-April-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>14-April-2026</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>14-April-2026</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>349</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>13-April-2026</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>mimoto</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>349</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>294</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AB11" t="n">
+        <v/>
+      </c>
+      <c r="AC11" t="n">
+        <v/>
+      </c>
+      <c r="AD11" t="n">
+        <v/>
+      </c>
+      <c r="AE11" t="n">
+        <v/>
+      </c>
+      <c r="AF11" t="n">
+        <v/>
+      </c>
+      <c r="AG11" t="n">
+        <v/>
+      </c>
+      <c r="AH11" t="n">
+        <v/>
+      </c>
+      <c r="AI11" t="n">
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>16-April-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>14-April-2026</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>14-April-2026</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>13-April-2026</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>345</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="AB12" t="n">
+        <v/>
+      </c>
+      <c r="AC12" t="n">
+        <v/>
+      </c>
+      <c r="AD12" t="n">
+        <v/>
+      </c>
+      <c r="AE12" t="n">
+        <v/>
+      </c>
+      <c r="AF12" t="n">
+        <v/>
+      </c>
+      <c r="AG12" t="n">
+        <v/>
+      </c>
+      <c r="AH12" t="n">
+        <v/>
+      </c>
+      <c r="AI12" t="n">
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>16-April-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>14-April-2026</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>1141</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>14-April-2026</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>1140</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>13-April-2026</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v/>
+      </c>
+      <c r="AC13" t="n">
+        <v/>
+      </c>
+      <c r="AD13" t="n">
+        <v/>
+      </c>
+      <c r="AE13" t="n">
+        <v/>
+      </c>
+      <c r="AF13" t="n">
+        <v/>
+      </c>
+      <c r="AG13" t="n">
+        <v/>
+      </c>
+      <c r="AH13" t="n">
+        <v/>
+      </c>
+      <c r="AI13" t="n">
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>16-April-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>14-April-2026</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>14-April-2026</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>168</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>13-April-2026</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>1141</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="Y14" t="inlineStr">
         <is>
           <t>0</t>
@@ -2535,119 +2888,143 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB14" t="n">
+        <v/>
+      </c>
+      <c r="AC14" t="n">
+        <v/>
+      </c>
+      <c r="AD14" t="n">
+        <v/>
+      </c>
+      <c r="AE14" t="n">
+        <v/>
+      </c>
+      <c r="AF14" t="n">
+        <v/>
+      </c>
+      <c r="AG14" t="n">
+        <v/>
+      </c>
+      <c r="AH14" t="n">
+        <v/>
+      </c>
+      <c r="AI14" t="n">
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>16-April-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>14-April-2026</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
         <is>
           <t>adminui</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>14-April-2026</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>adminui</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>13-April-2026</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="Y15" t="inlineStr">
         <is>
           <t>0</t>
@@ -2657,96 +3034,160 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB15" t="n">
+        <v/>
+      </c>
+      <c r="AC15" t="n">
+        <v/>
+      </c>
+      <c r="AD15" t="n">
+        <v/>
+      </c>
+      <c r="AE15" t="n">
+        <v/>
+      </c>
+      <c r="AF15" t="n">
+        <v/>
+      </c>
+      <c r="AG15" t="n">
+        <v/>
+      </c>
+      <c r="AH15" t="n">
+        <v/>
+      </c>
+      <c r="AI15" t="n">
+        <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v/>
-      </c>
-      <c r="B16" t="n">
-        <v/>
-      </c>
-      <c r="C16" t="n">
-        <v/>
-      </c>
-      <c r="D16" t="n">
-        <v/>
-      </c>
-      <c r="E16" t="n">
-        <v/>
-      </c>
-      <c r="F16" t="n">
-        <v/>
-      </c>
-      <c r="G16" t="n">
-        <v/>
-      </c>
-      <c r="H16" t="n">
-        <v/>
-      </c>
-      <c r="J16" t="n">
-        <v/>
-      </c>
-      <c r="K16" t="n">
-        <v/>
-      </c>
-      <c r="L16" t="n">
-        <v/>
-      </c>
-      <c r="M16" t="n">
-        <v/>
-      </c>
-      <c r="N16" t="n">
-        <v/>
-      </c>
-      <c r="O16" t="n">
-        <v/>
-      </c>
-      <c r="P16" t="n">
-        <v/>
-      </c>
-      <c r="Q16" t="n">
-        <v/>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>13-April-2026</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>16-April-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>adminui</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>15-April-2026</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adminui</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S16" t="n">
+        <v/>
+      </c>
+      <c r="T16" t="n">
+        <v/>
+      </c>
+      <c r="U16" t="n">
+        <v/>
+      </c>
+      <c r="V16" t="n">
+        <v/>
+      </c>
+      <c r="W16" t="n">
+        <v/>
+      </c>
+      <c r="X16" t="n">
+        <v/>
+      </c>
+      <c r="Y16" t="n">
+        <v/>
+      </c>
+      <c r="Z16" t="n">
+        <v/>
+      </c>
+      <c r="AB16" t="n">
+        <v/>
+      </c>
+      <c r="AC16" t="n">
+        <v/>
+      </c>
+      <c r="AD16" t="n">
+        <v/>
+      </c>
+      <c r="AE16" t="n">
+        <v/>
+      </c>
+      <c r="AF16" t="n">
+        <v/>
+      </c>
+      <c r="AG16" t="n">
+        <v/>
+      </c>
+      <c r="AH16" t="n">
+        <v/>
+      </c>
+      <c r="AI16" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/released.xlsx
+++ b/minio-report-tracker/xlxs/released.xlsx
@@ -824,9 +824,9 @@
     <col width="6" customWidth="1" min="21" max="21"/>
     <col width="6" customWidth="1" min="22" max="22"/>
     <col width="5" customWidth="1" min="23" max="23"/>
-    <col width="5" customWidth="1" min="24" max="24"/>
-    <col width="5" customWidth="1" min="25" max="25"/>
-    <col width="5" customWidth="1" min="26" max="26"/>
+    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
     <col width="2" customWidth="1" min="27" max="27"/>
     <col width="15" customWidth="1" min="28" max="28"/>
     <col width="9" customWidth="1" min="29" max="29"/>
@@ -1003,129 +1003,129 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13-April-2026</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
           <t>adminui</t>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
@@ -1165,87 +1165,87 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>14-April-2026</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1311,87 +1311,87 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>injiverify</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>14-April-2026</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1457,87 +1457,87 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>14-April-2026</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1603,87 +1603,87 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>943</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>14-April-2026</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1749,87 +1749,87 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>14-April-2026</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1895,87 +1895,87 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>masterdata-hin</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>masterdata-hin</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>masterdata-hin</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>14-April-2026</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -2041,87 +2041,87 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>masterdata-kan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>masterdata-kan</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>masterdata-kan</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>14-April-2026</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -2187,112 +2187,112 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>masterdata-tam</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>masterdata-tam</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>masterdata-tam</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>928</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>14-April-2026</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>masterdata-tam</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -2333,122 +2333,122 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>294</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>294</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>14-April-2026</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>349</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="AB11" t="n">
@@ -2479,122 +2479,122 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>14-April-2026</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="AB12" t="n">
@@ -2625,122 +2625,122 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>14-April-2026</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>1140</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="AB13" t="n">
@@ -2771,112 +2771,112 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
         <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>14-April-2026</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>34</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2917,112 +2917,112 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>76</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>99</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
         <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>167</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
         <is>
           <t>35</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>14-April-2026</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>adminui</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -3063,107 +3063,123 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>adminui</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>adminui</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
         <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>adminui</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" t="n">
-        <v/>
-      </c>
-      <c r="T16" t="n">
-        <v/>
-      </c>
-      <c r="U16" t="n">
-        <v/>
-      </c>
-      <c r="V16" t="n">
-        <v/>
-      </c>
-      <c r="W16" t="n">
-        <v/>
-      </c>
-      <c r="X16" t="n">
-        <v/>
-      </c>
-      <c r="Y16" t="n">
-        <v/>
-      </c>
-      <c r="Z16" t="n">
-        <v/>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="AB16" t="n">
         <v/>

--- a/minio-report-tracker/xlxs/released.xlsx
+++ b/minio-report-tracker/xlxs/released.xlsx
@@ -811,13 +811,13 @@
     <col width="4" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
-    <col width="5" customWidth="1" min="12" max="12"/>
-    <col width="5" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
     <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="5" customWidth="1" min="15" max="15"/>
-    <col width="5" customWidth="1" min="16" max="16"/>
-    <col width="5" customWidth="1" min="17" max="17"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -905,1007 +905,1231 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>17-April-2026</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adminui</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v/>
-      </c>
-      <c r="K3" t="n">
-        <v/>
-      </c>
-      <c r="L3" t="n">
-        <v/>
-      </c>
-      <c r="M3" t="n">
-        <v/>
-      </c>
-      <c r="N3" t="n">
-        <v/>
-      </c>
-      <c r="O3" t="n">
-        <v/>
-      </c>
-      <c r="P3" t="n">
-        <v/>
-      </c>
-      <c r="Q3" t="n">
-        <v/>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v/>
-      </c>
-      <c r="K4" t="n">
-        <v/>
-      </c>
-      <c r="L4" t="n">
-        <v/>
-      </c>
-      <c r="M4" t="n">
-        <v/>
-      </c>
-      <c r="N4" t="n">
-        <v/>
-      </c>
-      <c r="O4" t="n">
-        <v/>
-      </c>
-      <c r="P4" t="n">
-        <v/>
-      </c>
-      <c r="Q4" t="n">
-        <v/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v/>
-      </c>
-      <c r="K5" t="n">
-        <v/>
-      </c>
-      <c r="L5" t="n">
-        <v/>
-      </c>
-      <c r="M5" t="n">
-        <v/>
-      </c>
-      <c r="N5" t="n">
-        <v/>
-      </c>
-      <c r="O5" t="n">
-        <v/>
-      </c>
-      <c r="P5" t="n">
-        <v/>
-      </c>
-      <c r="Q5" t="n">
-        <v/>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v/>
-      </c>
-      <c r="K6" t="n">
-        <v/>
-      </c>
-      <c r="L6" t="n">
-        <v/>
-      </c>
-      <c r="M6" t="n">
-        <v/>
-      </c>
-      <c r="N6" t="n">
-        <v/>
-      </c>
-      <c r="O6" t="n">
-        <v/>
-      </c>
-      <c r="P6" t="n">
-        <v/>
-      </c>
-      <c r="Q6" t="n">
-        <v/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v/>
-      </c>
-      <c r="K7" t="n">
-        <v/>
-      </c>
-      <c r="L7" t="n">
-        <v/>
-      </c>
-      <c r="M7" t="n">
-        <v/>
-      </c>
-      <c r="N7" t="n">
-        <v/>
-      </c>
-      <c r="O7" t="n">
-        <v/>
-      </c>
-      <c r="P7" t="n">
-        <v/>
-      </c>
-      <c r="Q7" t="n">
-        <v/>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>masterdata-hin</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>masterdata-hin</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v/>
-      </c>
-      <c r="K8" t="n">
-        <v/>
-      </c>
-      <c r="L8" t="n">
-        <v/>
-      </c>
-      <c r="M8" t="n">
-        <v/>
-      </c>
-      <c r="N8" t="n">
-        <v/>
-      </c>
-      <c r="O8" t="n">
-        <v/>
-      </c>
-      <c r="P8" t="n">
-        <v/>
-      </c>
-      <c r="Q8" t="n">
-        <v/>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>masterdata-kan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>928</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>masterdata-kan</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v/>
-      </c>
-      <c r="K9" t="n">
-        <v/>
-      </c>
-      <c r="L9" t="n">
-        <v/>
-      </c>
-      <c r="M9" t="n">
-        <v/>
-      </c>
-      <c r="N9" t="n">
-        <v/>
-      </c>
-      <c r="O9" t="n">
-        <v/>
-      </c>
-      <c r="P9" t="n">
-        <v/>
-      </c>
-      <c r="Q9" t="n">
-        <v/>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>masterdata-tam</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>928</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>masterdata-tam</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v/>
-      </c>
-      <c r="K10" t="n">
-        <v/>
-      </c>
-      <c r="L10" t="n">
-        <v/>
-      </c>
-      <c r="M10" t="n">
-        <v/>
-      </c>
-      <c r="N10" t="n">
-        <v/>
-      </c>
-      <c r="O10" t="n">
-        <v/>
-      </c>
-      <c r="P10" t="n">
-        <v/>
-      </c>
-      <c r="Q10" t="n">
-        <v/>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>312</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
-      </c>
-      <c r="J11" t="n">
-        <v/>
-      </c>
-      <c r="K11" t="n">
-        <v/>
-      </c>
-      <c r="L11" t="n">
-        <v/>
-      </c>
-      <c r="M11" t="n">
-        <v/>
-      </c>
-      <c r="N11" t="n">
-        <v/>
-      </c>
-      <c r="O11" t="n">
-        <v/>
-      </c>
-      <c r="P11" t="n">
-        <v/>
-      </c>
-      <c r="Q11" t="n">
-        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
-      </c>
-      <c r="J12" t="n">
-        <v/>
-      </c>
-      <c r="K12" t="n">
-        <v/>
-      </c>
-      <c r="L12" t="n">
-        <v/>
-      </c>
-      <c r="M12" t="n">
-        <v/>
-      </c>
-      <c r="N12" t="n">
-        <v/>
-      </c>
-      <c r="O12" t="n">
-        <v/>
-      </c>
-      <c r="P12" t="n">
-        <v/>
-      </c>
-      <c r="Q12" t="n">
-        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
-      </c>
-      <c r="J13" t="n">
-        <v/>
-      </c>
-      <c r="K13" t="n">
-        <v/>
-      </c>
-      <c r="L13" t="n">
-        <v/>
-      </c>
-      <c r="M13" t="n">
-        <v/>
-      </c>
-      <c r="N13" t="n">
-        <v/>
-      </c>
-      <c r="O13" t="n">
-        <v/>
-      </c>
-      <c r="P13" t="n">
-        <v/>
-      </c>
-      <c r="Q13" t="n">
-        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>1140</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v/>
-      </c>
-      <c r="K14" t="n">
-        <v/>
-      </c>
-      <c r="L14" t="n">
-        <v/>
-      </c>
-      <c r="M14" t="n">
-        <v/>
-      </c>
-      <c r="N14" t="n">
-        <v/>
-      </c>
-      <c r="O14" t="n">
-        <v/>
-      </c>
-      <c r="P14" t="n">
-        <v/>
-      </c>
-      <c r="Q14" t="n">
-        <v/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>201</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v/>
-      </c>
-      <c r="K15" t="n">
-        <v/>
-      </c>
-      <c r="L15" t="n">
-        <v/>
-      </c>
-      <c r="M15" t="n">
-        <v/>
-      </c>
-      <c r="N15" t="n">
-        <v/>
-      </c>
-      <c r="O15" t="n">
-        <v/>
-      </c>
-      <c r="P15" t="n">
-        <v/>
-      </c>
-      <c r="Q15" t="n">
-        <v/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>adminui</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>adminui</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v/>
-      </c>
-      <c r="K16" t="n">
-        <v/>
-      </c>
-      <c r="L16" t="n">
-        <v/>
-      </c>
-      <c r="M16" t="n">
-        <v/>
-      </c>
-      <c r="N16" t="n">
-        <v/>
-      </c>
-      <c r="O16" t="n">
-        <v/>
-      </c>
-      <c r="P16" t="n">
-        <v/>
-      </c>
-      <c r="Q16" t="n">
-        <v/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/released.xlsx
+++ b/minio-report-tracker/xlxs/released.xlsx
@@ -798,7 +798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:Z16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -818,6 +818,15 @@
     <col width="4" customWidth="1" min="15" max="15"/>
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="2" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
+    <col width="5" customWidth="1" min="23" max="23"/>
+    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -901,84 +910,164 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -987,80 +1076,120 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1069,80 +1198,120 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1151,80 +1320,120 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1233,80 +1442,120 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1315,80 +1564,120 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1397,80 +1686,120 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>masterdata-hin</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>masterdata-hin</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>masterdata-hin</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1479,80 +1808,120 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>masterdata-kan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>masterdata-kan</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>928</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>masterdata-kan</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1561,80 +1930,120 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>masterdata-tam</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>masterdata-tam</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>928</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>masterdata-tam</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1643,80 +2052,120 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>312</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>312</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1725,80 +2174,120 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -1807,80 +2296,120 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1889,80 +2418,120 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1136</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>1140</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1971,80 +2540,120 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>201</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>201</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -2053,80 +2662,120 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>adminui</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>adminui</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>adminui</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/minio-report-tracker/xlxs/released.xlsx
+++ b/minio-report-tracker/xlxs/released.xlsx
@@ -798,7 +798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z16"/>
+  <dimension ref="A1:AI16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -827,6 +827,15 @@
     <col width="4" customWidth="1" min="24" max="24"/>
     <col width="4" customWidth="1" min="25" max="25"/>
     <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="2" customWidth="1" min="27" max="27"/>
+    <col width="15" customWidth="1" min="28" max="28"/>
+    <col width="9" customWidth="1" min="29" max="29"/>
+    <col width="5" customWidth="1" min="30" max="30"/>
+    <col width="5" customWidth="1" min="31" max="31"/>
+    <col width="5" customWidth="1" min="32" max="32"/>
+    <col width="5" customWidth="1" min="33" max="33"/>
+    <col width="5" customWidth="1" min="34" max="34"/>
+    <col width="5" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -950,362 +959,466 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>9</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>adminui</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
       <c r="Z3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB3" t="n">
+        <v/>
+      </c>
+      <c r="AC3" t="n">
+        <v/>
+      </c>
+      <c r="AD3" t="n">
+        <v/>
+      </c>
+      <c r="AE3" t="n">
+        <v/>
+      </c>
+      <c r="AF3" t="n">
+        <v/>
+      </c>
+      <c r="AG3" t="n">
+        <v/>
+      </c>
+      <c r="AH3" t="n">
+        <v/>
+      </c>
+      <c r="AI3" t="n">
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>injiverify</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="Y4" t="inlineStr">
         <is>
           <t>0</t>
@@ -1315,241 +1428,289 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB4" t="n">
+        <v/>
+      </c>
+      <c r="AC4" t="n">
+        <v/>
+      </c>
+      <c r="AD4" t="n">
+        <v/>
+      </c>
+      <c r="AE4" t="n">
+        <v/>
+      </c>
+      <c r="AF4" t="n">
+        <v/>
+      </c>
+      <c r="AG4" t="n">
+        <v/>
+      </c>
+      <c r="AH4" t="n">
+        <v/>
+      </c>
+      <c r="AI4" t="n">
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="Z5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB5" t="n">
+        <v/>
+      </c>
+      <c r="AC5" t="n">
+        <v/>
+      </c>
+      <c r="AD5" t="n">
+        <v/>
+      </c>
+      <c r="AE5" t="n">
+        <v/>
+      </c>
+      <c r="AF5" t="n">
+        <v/>
+      </c>
+      <c r="AG5" t="n">
+        <v/>
+      </c>
+      <c r="AH5" t="n">
+        <v/>
+      </c>
+      <c r="AI5" t="n">
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="Y6" t="inlineStr">
         <is>
           <t>0</t>
@@ -1559,973 +1720,1165 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB6" t="n">
+        <v/>
+      </c>
+      <c r="AC6" t="n">
+        <v/>
+      </c>
+      <c r="AD6" t="n">
+        <v/>
+      </c>
+      <c r="AE6" t="n">
+        <v/>
+      </c>
+      <c r="AF6" t="n">
+        <v/>
+      </c>
+      <c r="AG6" t="n">
+        <v/>
+      </c>
+      <c r="AH6" t="n">
+        <v/>
+      </c>
+      <c r="AI6" t="n">
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="Z7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB7" t="n">
+        <v/>
+      </c>
+      <c r="AC7" t="n">
+        <v/>
+      </c>
+      <c r="AD7" t="n">
+        <v/>
+      </c>
+      <c r="AE7" t="n">
+        <v/>
+      </c>
+      <c r="AF7" t="n">
+        <v/>
+      </c>
+      <c r="AG7" t="n">
+        <v/>
+      </c>
+      <c r="AH7" t="n">
+        <v/>
+      </c>
+      <c r="AI7" t="n">
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>masterdata-hin</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>masterdata-hin</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>masterdata-hin</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>masterdata-hin</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="Z8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB8" t="n">
+        <v/>
+      </c>
+      <c r="AC8" t="n">
+        <v/>
+      </c>
+      <c r="AD8" t="n">
+        <v/>
+      </c>
+      <c r="AE8" t="n">
+        <v/>
+      </c>
+      <c r="AF8" t="n">
+        <v/>
+      </c>
+      <c r="AG8" t="n">
+        <v/>
+      </c>
+      <c r="AH8" t="n">
+        <v/>
+      </c>
+      <c r="AI8" t="n">
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>masterdata-kan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>masterdata-kan</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>masterdata-kan</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>928</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>masterdata-kan</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="Z9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB9" t="n">
+        <v/>
+      </c>
+      <c r="AC9" t="n">
+        <v/>
+      </c>
+      <c r="AD9" t="n">
+        <v/>
+      </c>
+      <c r="AE9" t="n">
+        <v/>
+      </c>
+      <c r="AF9" t="n">
+        <v/>
+      </c>
+      <c r="AG9" t="n">
+        <v/>
+      </c>
+      <c r="AH9" t="n">
+        <v/>
+      </c>
+      <c r="AI9" t="n">
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>masterdata-tam</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>masterdata-tam</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>masterdata-tam</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>928</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>masterdata-tam</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="Z10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB10" t="n">
+        <v/>
+      </c>
+      <c r="AC10" t="n">
+        <v/>
+      </c>
+      <c r="AD10" t="n">
+        <v/>
+      </c>
+      <c r="AE10" t="n">
+        <v/>
+      </c>
+      <c r="AF10" t="n">
+        <v/>
+      </c>
+      <c r="AG10" t="n">
+        <v/>
+      </c>
+      <c r="AH10" t="n">
+        <v/>
+      </c>
+      <c r="AI10" t="n">
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>311</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>312</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>mimoto</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>349</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>312</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AB11" t="n">
+        <v/>
+      </c>
+      <c r="AC11" t="n">
+        <v/>
+      </c>
+      <c r="AD11" t="n">
+        <v/>
+      </c>
+      <c r="AE11" t="n">
+        <v/>
+      </c>
+      <c r="AF11" t="n">
+        <v/>
+      </c>
+      <c r="AG11" t="n">
+        <v/>
+      </c>
+      <c r="AH11" t="n">
+        <v/>
+      </c>
+      <c r="AI11" t="n">
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>349</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="AB12" t="n">
+        <v/>
+      </c>
+      <c r="AC12" t="n">
+        <v/>
+      </c>
+      <c r="AD12" t="n">
+        <v/>
+      </c>
+      <c r="AE12" t="n">
+        <v/>
+      </c>
+      <c r="AF12" t="n">
+        <v/>
+      </c>
+      <c r="AG12" t="n">
+        <v/>
+      </c>
+      <c r="AH12" t="n">
+        <v/>
+      </c>
+      <c r="AI12" t="n">
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AB13" t="n">
+        <v/>
+      </c>
+      <c r="AC13" t="n">
+        <v/>
+      </c>
+      <c r="AD13" t="n">
+        <v/>
+      </c>
+      <c r="AE13" t="n">
+        <v/>
+      </c>
+      <c r="AF13" t="n">
+        <v/>
+      </c>
+      <c r="AG13" t="n">
+        <v/>
+      </c>
+      <c r="AH13" t="n">
+        <v/>
+      </c>
+      <c r="AI13" t="n">
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>1136</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>1140</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="Y14" t="inlineStr">
         <is>
           <t>0</t>
@@ -2535,119 +2888,143 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB14" t="n">
+        <v/>
+      </c>
+      <c r="AC14" t="n">
+        <v/>
+      </c>
+      <c r="AD14" t="n">
+        <v/>
+      </c>
+      <c r="AE14" t="n">
+        <v/>
+      </c>
+      <c r="AF14" t="n">
+        <v/>
+      </c>
+      <c r="AG14" t="n">
+        <v/>
+      </c>
+      <c r="AH14" t="n">
+        <v/>
+      </c>
+      <c r="AI14" t="n">
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>202</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>201</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="Y15" t="inlineStr">
         <is>
           <t>0</t>
@@ -2657,119 +3034,143 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB15" t="n">
+        <v/>
+      </c>
+      <c r="AC15" t="n">
+        <v/>
+      </c>
+      <c r="AD15" t="n">
+        <v/>
+      </c>
+      <c r="AE15" t="n">
+        <v/>
+      </c>
+      <c r="AF15" t="n">
+        <v/>
+      </c>
+      <c r="AG15" t="n">
+        <v/>
+      </c>
+      <c r="AH15" t="n">
+        <v/>
+      </c>
+      <c r="AI15" t="n">
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>adminui</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>adminui</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>adminui</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>adminui</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="Y16" t="inlineStr">
         <is>
           <t>0</t>
@@ -2779,6 +3180,30 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB16" t="n">
+        <v/>
+      </c>
+      <c r="AC16" t="n">
+        <v/>
+      </c>
+      <c r="AD16" t="n">
+        <v/>
+      </c>
+      <c r="AE16" t="n">
+        <v/>
+      </c>
+      <c r="AF16" t="n">
+        <v/>
+      </c>
+      <c r="AG16" t="n">
+        <v/>
+      </c>
+      <c r="AH16" t="n">
+        <v/>
+      </c>
+      <c r="AI16" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/released.xlsx
+++ b/minio-report-tracker/xlxs/released.xlsx
@@ -806,7 +806,7 @@
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
     <col width="4" customWidth="1" min="7" max="7"/>
     <col width="4" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
@@ -1003,127 +1003,127 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>24-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>21-April-2026</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1165,87 +1165,87 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>24-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>22-April-2026</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>21-April-2026</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1311,87 +1311,87 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>24-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>22-April-2026</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>injiverify</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>21-April-2026</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1457,87 +1457,87 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>24-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>22-April-2026</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>21-April-2026</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1603,87 +1603,87 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>24-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>22-April-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>21-April-2026</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1749,87 +1749,87 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>24-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>22-April-2026</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>21-April-2026</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1895,87 +1895,87 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>24-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>masterdata-hin</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>928</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>masterdata-hin</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>22-April-2026</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>masterdata-hin</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>21-April-2026</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -2041,112 +2041,112 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>24-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>masterdata-kan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>masterdata-kan</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>masterdata-kan</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>21-April-2026</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>masterdata-kan</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>928</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -2187,112 +2187,112 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>24-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>masterdata-tam</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>masterdata-tam</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>masterdata-tam</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>21-April-2026</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>masterdata-tam</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>928</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -2333,112 +2333,112 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>24-April-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>312</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>311</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>21-April-2026</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>mimoto</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>349</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>312</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -2479,87 +2479,87 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>24-April-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>22-April-2026</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>349</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>21-April-2026</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -2625,87 +2625,87 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>24-April-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>22-April-2026</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>21-April-2026</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
@@ -2771,112 +2771,112 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>24-April-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>1136</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>21-April-2026</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>1141</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2917,104 +2917,104 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>24-April-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>86</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>202</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>21-April-2026</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
       <c r="W15" t="inlineStr">
         <is>
           <t>0</t>
@@ -3022,7 +3022,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -3063,87 +3063,87 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>24-April-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>adminui</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>adminui</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
         <is>
           <t>22-April-2026</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>adminui</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>21-April-2026</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">

--- a/minio-report-tracker/xlxs/released.xlsx
+++ b/minio-report-tracker/xlxs/released.xlsx
@@ -811,13 +811,13 @@
     <col width="4" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
-    <col width="5" customWidth="1" min="12" max="12"/>
-    <col width="5" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
     <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="5" customWidth="1" min="15" max="15"/>
-    <col width="5" customWidth="1" min="16" max="16"/>
-    <col width="5" customWidth="1" min="17" max="17"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -905,159 +905,159 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>28-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>24-April-2026</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>28-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>24-April-2026</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adminui</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -1069,859 +1069,1067 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>28-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v/>
-      </c>
-      <c r="K4" t="n">
-        <v/>
-      </c>
-      <c r="L4" t="n">
-        <v/>
-      </c>
-      <c r="M4" t="n">
-        <v/>
-      </c>
-      <c r="N4" t="n">
-        <v/>
-      </c>
-      <c r="O4" t="n">
-        <v/>
-      </c>
-      <c r="P4" t="n">
-        <v/>
-      </c>
-      <c r="Q4" t="n">
-        <v/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>28-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v/>
-      </c>
-      <c r="K5" t="n">
-        <v/>
-      </c>
-      <c r="L5" t="n">
-        <v/>
-      </c>
-      <c r="M5" t="n">
-        <v/>
-      </c>
-      <c r="N5" t="n">
-        <v/>
-      </c>
-      <c r="O5" t="n">
-        <v/>
-      </c>
-      <c r="P5" t="n">
-        <v/>
-      </c>
-      <c r="Q5" t="n">
-        <v/>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>28-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v/>
-      </c>
-      <c r="K6" t="n">
-        <v/>
-      </c>
-      <c r="L6" t="n">
-        <v/>
-      </c>
-      <c r="M6" t="n">
-        <v/>
-      </c>
-      <c r="N6" t="n">
-        <v/>
-      </c>
-      <c r="O6" t="n">
-        <v/>
-      </c>
-      <c r="P6" t="n">
-        <v/>
-      </c>
-      <c r="Q6" t="n">
-        <v/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>28-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v/>
-      </c>
-      <c r="K7" t="n">
-        <v/>
-      </c>
-      <c r="L7" t="n">
-        <v/>
-      </c>
-      <c r="M7" t="n">
-        <v/>
-      </c>
-      <c r="N7" t="n">
-        <v/>
-      </c>
-      <c r="O7" t="n">
-        <v/>
-      </c>
-      <c r="P7" t="n">
-        <v/>
-      </c>
-      <c r="Q7" t="n">
-        <v/>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>28-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>masterdata-hin</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>masterdata-hin</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v/>
-      </c>
-      <c r="K8" t="n">
-        <v/>
-      </c>
-      <c r="L8" t="n">
-        <v/>
-      </c>
-      <c r="M8" t="n">
-        <v/>
-      </c>
-      <c r="N8" t="n">
-        <v/>
-      </c>
-      <c r="O8" t="n">
-        <v/>
-      </c>
-      <c r="P8" t="n">
-        <v/>
-      </c>
-      <c r="Q8" t="n">
-        <v/>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>28-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>masterdata-kan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>masterdata-kan</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v/>
-      </c>
-      <c r="K9" t="n">
-        <v/>
-      </c>
-      <c r="L9" t="n">
-        <v/>
-      </c>
-      <c r="M9" t="n">
-        <v/>
-      </c>
-      <c r="N9" t="n">
-        <v/>
-      </c>
-      <c r="O9" t="n">
-        <v/>
-      </c>
-      <c r="P9" t="n">
-        <v/>
-      </c>
-      <c r="Q9" t="n">
-        <v/>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>28-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>masterdata-tam</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>masterdata-tam</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>928</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v/>
-      </c>
-      <c r="K10" t="n">
-        <v/>
-      </c>
-      <c r="L10" t="n">
-        <v/>
-      </c>
-      <c r="M10" t="n">
-        <v/>
-      </c>
-      <c r="N10" t="n">
-        <v/>
-      </c>
-      <c r="O10" t="n">
-        <v/>
-      </c>
-      <c r="P10" t="n">
-        <v/>
-      </c>
-      <c r="Q10" t="n">
-        <v/>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>28-April-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>312</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
-      </c>
-      <c r="J11" t="n">
-        <v/>
-      </c>
-      <c r="K11" t="n">
-        <v/>
-      </c>
-      <c r="L11" t="n">
-        <v/>
-      </c>
-      <c r="M11" t="n">
-        <v/>
-      </c>
-      <c r="N11" t="n">
-        <v/>
-      </c>
-      <c r="O11" t="n">
-        <v/>
-      </c>
-      <c r="P11" t="n">
-        <v/>
-      </c>
-      <c r="Q11" t="n">
-        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>28-April-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
-      </c>
-      <c r="J12" t="n">
-        <v/>
-      </c>
-      <c r="K12" t="n">
-        <v/>
-      </c>
-      <c r="L12" t="n">
-        <v/>
-      </c>
-      <c r="M12" t="n">
-        <v/>
-      </c>
-      <c r="N12" t="n">
-        <v/>
-      </c>
-      <c r="O12" t="n">
-        <v/>
-      </c>
-      <c r="P12" t="n">
-        <v/>
-      </c>
-      <c r="Q12" t="n">
-        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>28-April-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
-      </c>
-      <c r="J13" t="n">
-        <v/>
-      </c>
-      <c r="K13" t="n">
-        <v/>
-      </c>
-      <c r="L13" t="n">
-        <v/>
-      </c>
-      <c r="M13" t="n">
-        <v/>
-      </c>
-      <c r="N13" t="n">
-        <v/>
-      </c>
-      <c r="O13" t="n">
-        <v/>
-      </c>
-      <c r="P13" t="n">
-        <v/>
-      </c>
-      <c r="Q13" t="n">
-        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>28-April-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1131</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v/>
-      </c>
-      <c r="K14" t="n">
-        <v/>
-      </c>
-      <c r="L14" t="n">
-        <v/>
-      </c>
-      <c r="M14" t="n">
-        <v/>
-      </c>
-      <c r="N14" t="n">
-        <v/>
-      </c>
-      <c r="O14" t="n">
-        <v/>
-      </c>
-      <c r="P14" t="n">
-        <v/>
-      </c>
-      <c r="Q14" t="n">
-        <v/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>28-April-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>115</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v/>
-      </c>
-      <c r="K15" t="n">
-        <v/>
-      </c>
-      <c r="L15" t="n">
-        <v/>
-      </c>
-      <c r="M15" t="n">
-        <v/>
-      </c>
-      <c r="N15" t="n">
-        <v/>
-      </c>
-      <c r="O15" t="n">
-        <v/>
-      </c>
-      <c r="P15" t="n">
-        <v/>
-      </c>
-      <c r="Q15" t="n">
-        <v/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>28-April-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>adminui</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>adminui</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v/>
-      </c>
-      <c r="K16" t="n">
-        <v/>
-      </c>
-      <c r="L16" t="n">
-        <v/>
-      </c>
-      <c r="M16" t="n">
-        <v/>
-      </c>
-      <c r="N16" t="n">
-        <v/>
-      </c>
-      <c r="O16" t="n">
-        <v/>
-      </c>
-      <c r="P16" t="n">
-        <v/>
-      </c>
-      <c r="Q16" t="n">
-        <v/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/released.xlsx
+++ b/minio-report-tracker/xlxs/released.xlsx
@@ -798,7 +798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:Z16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -818,6 +818,15 @@
     <col width="4" customWidth="1" min="15" max="15"/>
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="2" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
+    <col width="5" customWidth="1" min="23" max="23"/>
+    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -901,84 +910,164 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>29-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -987,80 +1076,120 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>29-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1069,80 +1198,120 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>29-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1151,80 +1320,120 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>29-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1233,80 +1442,120 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>29-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1315,80 +1564,120 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>29-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1397,80 +1686,120 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>29-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>masterdata-hin</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>masterdata-hin</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>masterdata-hin</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1479,80 +1808,120 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>29-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>masterdata-kan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>928</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>masterdata-kan</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>masterdata-kan</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1561,80 +1930,120 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>29-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>masterdata-tam</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>masterdata-tam</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>masterdata-tam</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>928</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1643,80 +2052,120 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>29-April-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>312</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>312</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1725,80 +2174,120 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>29-April-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>346</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -1807,80 +2296,120 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>29-April-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1889,80 +2418,120 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>29-April-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>1131</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1971,80 +2540,120 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>29-April-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>74</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>115</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -2053,80 +2662,120 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>29-April-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>adminui</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>adminui</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>adminui</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/minio-report-tracker/xlxs/released.xlsx
+++ b/minio-report-tracker/xlxs/released.xlsx
@@ -798,7 +798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z16"/>
+  <dimension ref="A1:AI16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -827,6 +827,15 @@
     <col width="4" customWidth="1" min="24" max="24"/>
     <col width="4" customWidth="1" min="25" max="25"/>
     <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="2" customWidth="1" min="27" max="27"/>
+    <col width="15" customWidth="1" min="28" max="28"/>
+    <col width="9" customWidth="1" min="29" max="29"/>
+    <col width="5" customWidth="1" min="30" max="30"/>
+    <col width="5" customWidth="1" min="31" max="31"/>
+    <col width="5" customWidth="1" min="32" max="32"/>
+    <col width="5" customWidth="1" min="33" max="33"/>
+    <col width="5" customWidth="1" min="34" max="34"/>
+    <col width="5" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -950,362 +959,466 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>30-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>9</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>adminui</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>30-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>27-April-2026</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
       <c r="Z3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB3" t="n">
+        <v/>
+      </c>
+      <c r="AC3" t="n">
+        <v/>
+      </c>
+      <c r="AD3" t="n">
+        <v/>
+      </c>
+      <c r="AE3" t="n">
+        <v/>
+      </c>
+      <c r="AF3" t="n">
+        <v/>
+      </c>
+      <c r="AG3" t="n">
+        <v/>
+      </c>
+      <c r="AH3" t="n">
+        <v/>
+      </c>
+      <c r="AI3" t="n">
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>30-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>27-April-2026</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>injiverify</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="Y4" t="inlineStr">
         <is>
           <t>0</t>
@@ -1315,241 +1428,289 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB4" t="n">
+        <v/>
+      </c>
+      <c r="AC4" t="n">
+        <v/>
+      </c>
+      <c r="AD4" t="n">
+        <v/>
+      </c>
+      <c r="AE4" t="n">
+        <v/>
+      </c>
+      <c r="AF4" t="n">
+        <v/>
+      </c>
+      <c r="AG4" t="n">
+        <v/>
+      </c>
+      <c r="AH4" t="n">
+        <v/>
+      </c>
+      <c r="AI4" t="n">
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>30-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>27-April-2026</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="Z5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB5" t="n">
+        <v/>
+      </c>
+      <c r="AC5" t="n">
+        <v/>
+      </c>
+      <c r="AD5" t="n">
+        <v/>
+      </c>
+      <c r="AE5" t="n">
+        <v/>
+      </c>
+      <c r="AF5" t="n">
+        <v/>
+      </c>
+      <c r="AG5" t="n">
+        <v/>
+      </c>
+      <c r="AH5" t="n">
+        <v/>
+      </c>
+      <c r="AI5" t="n">
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>30-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>27-April-2026</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="Y6" t="inlineStr">
         <is>
           <t>0</t>
@@ -1559,973 +1720,1165 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB6" t="n">
+        <v/>
+      </c>
+      <c r="AC6" t="n">
+        <v/>
+      </c>
+      <c r="AD6" t="n">
+        <v/>
+      </c>
+      <c r="AE6" t="n">
+        <v/>
+      </c>
+      <c r="AF6" t="n">
+        <v/>
+      </c>
+      <c r="AG6" t="n">
+        <v/>
+      </c>
+      <c r="AH6" t="n">
+        <v/>
+      </c>
+      <c r="AI6" t="n">
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>30-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>27-April-2026</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="Z7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB7" t="n">
+        <v/>
+      </c>
+      <c r="AC7" t="n">
+        <v/>
+      </c>
+      <c r="AD7" t="n">
+        <v/>
+      </c>
+      <c r="AE7" t="n">
+        <v/>
+      </c>
+      <c r="AF7" t="n">
+        <v/>
+      </c>
+      <c r="AG7" t="n">
+        <v/>
+      </c>
+      <c r="AH7" t="n">
+        <v/>
+      </c>
+      <c r="AI7" t="n">
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>30-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>masterdata-hin</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>masterdata-hin</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>masterdata-hin</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>27-April-2026</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>masterdata-hin</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="Z8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB8" t="n">
+        <v/>
+      </c>
+      <c r="AC8" t="n">
+        <v/>
+      </c>
+      <c r="AD8" t="n">
+        <v/>
+      </c>
+      <c r="AE8" t="n">
+        <v/>
+      </c>
+      <c r="AF8" t="n">
+        <v/>
+      </c>
+      <c r="AG8" t="n">
+        <v/>
+      </c>
+      <c r="AH8" t="n">
+        <v/>
+      </c>
+      <c r="AI8" t="n">
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>30-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>masterdata-kan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>masterdata-kan</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>928</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>masterdata-kan</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>27-April-2026</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>masterdata-kan</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="Z9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB9" t="n">
+        <v/>
+      </c>
+      <c r="AC9" t="n">
+        <v/>
+      </c>
+      <c r="AD9" t="n">
+        <v/>
+      </c>
+      <c r="AE9" t="n">
+        <v/>
+      </c>
+      <c r="AF9" t="n">
+        <v/>
+      </c>
+      <c r="AG9" t="n">
+        <v/>
+      </c>
+      <c r="AH9" t="n">
+        <v/>
+      </c>
+      <c r="AI9" t="n">
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>30-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>masterdata-tam</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>masterdata-tam</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>masterdata-tam</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>27-April-2026</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>masterdata-tam</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>928</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="Z10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB10" t="n">
+        <v/>
+      </c>
+      <c r="AC10" t="n">
+        <v/>
+      </c>
+      <c r="AD10" t="n">
+        <v/>
+      </c>
+      <c r="AE10" t="n">
+        <v/>
+      </c>
+      <c r="AF10" t="n">
+        <v/>
+      </c>
+      <c r="AG10" t="n">
+        <v/>
+      </c>
+      <c r="AH10" t="n">
+        <v/>
+      </c>
+      <c r="AI10" t="n">
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>30-April-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>312</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>312</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>27-April-2026</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>mimoto</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>349</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>312</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AB11" t="n">
+        <v/>
+      </c>
+      <c r="AC11" t="n">
+        <v/>
+      </c>
+      <c r="AD11" t="n">
+        <v/>
+      </c>
+      <c r="AE11" t="n">
+        <v/>
+      </c>
+      <c r="AF11" t="n">
+        <v/>
+      </c>
+      <c r="AG11" t="n">
+        <v/>
+      </c>
+      <c r="AH11" t="n">
+        <v/>
+      </c>
+      <c r="AI11" t="n">
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>30-April-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>346</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>27-April-2026</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>349</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="AB12" t="n">
+        <v/>
+      </c>
+      <c r="AC12" t="n">
+        <v/>
+      </c>
+      <c r="AD12" t="n">
+        <v/>
+      </c>
+      <c r="AE12" t="n">
+        <v/>
+      </c>
+      <c r="AF12" t="n">
+        <v/>
+      </c>
+      <c r="AG12" t="n">
+        <v/>
+      </c>
+      <c r="AH12" t="n">
+        <v/>
+      </c>
+      <c r="AI12" t="n">
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>30-April-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>27-April-2026</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AB13" t="n">
+        <v/>
+      </c>
+      <c r="AC13" t="n">
+        <v/>
+      </c>
+      <c r="AD13" t="n">
+        <v/>
+      </c>
+      <c r="AE13" t="n">
+        <v/>
+      </c>
+      <c r="AF13" t="n">
+        <v/>
+      </c>
+      <c r="AG13" t="n">
+        <v/>
+      </c>
+      <c r="AH13" t="n">
+        <v/>
+      </c>
+      <c r="AI13" t="n">
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>30-April-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>1131</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>27-April-2026</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>1141</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="Y14" t="inlineStr">
         <is>
           <t>0</t>
@@ -2535,119 +2888,143 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB14" t="n">
+        <v/>
+      </c>
+      <c r="AC14" t="n">
+        <v/>
+      </c>
+      <c r="AD14" t="n">
+        <v/>
+      </c>
+      <c r="AE14" t="n">
+        <v/>
+      </c>
+      <c r="AF14" t="n">
+        <v/>
+      </c>
+      <c r="AG14" t="n">
+        <v/>
+      </c>
+      <c r="AH14" t="n">
+        <v/>
+      </c>
+      <c r="AI14" t="n">
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>30-April-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>202</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>74</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>27-April-2026</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="Y15" t="inlineStr">
         <is>
           <t>0</t>
@@ -2657,109 +3034,133 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB15" t="n">
+        <v/>
+      </c>
+      <c r="AC15" t="n">
+        <v/>
+      </c>
+      <c r="AD15" t="n">
+        <v/>
+      </c>
+      <c r="AE15" t="n">
+        <v/>
+      </c>
+      <c r="AF15" t="n">
+        <v/>
+      </c>
+      <c r="AG15" t="n">
+        <v/>
+      </c>
+      <c r="AH15" t="n">
+        <v/>
+      </c>
+      <c r="AI15" t="n">
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>30-April-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>adminui</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>adminui</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>adminui</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>27-April-2026</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>adminui</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="W16" t="inlineStr">
         <is>
           <t>0</t>
@@ -2767,7 +3168,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2779,6 +3180,30 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB16" t="n">
+        <v/>
+      </c>
+      <c r="AC16" t="n">
+        <v/>
+      </c>
+      <c r="AD16" t="n">
+        <v/>
+      </c>
+      <c r="AE16" t="n">
+        <v/>
+      </c>
+      <c r="AF16" t="n">
+        <v/>
+      </c>
+      <c r="AG16" t="n">
+        <v/>
+      </c>
+      <c r="AH16" t="n">
+        <v/>
+      </c>
+      <c r="AI16" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/released.xlsx
+++ b/minio-report-tracker/xlxs/released.xlsx
@@ -801,7 +801,7 @@
   <dimension ref="A1:AI16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
@@ -1003,129 +1003,129 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>01-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>592</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>27-April-2026</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
           <t>adminui</t>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
@@ -1165,87 +1165,87 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>01-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>29-April-2026</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>28-April-2026</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1311,87 +1311,87 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>01-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>29-April-2026</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>injiverify</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>28-April-2026</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1457,87 +1457,87 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>01-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>29-April-2026</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>28-April-2026</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1603,87 +1603,87 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>01-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>29-April-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>28-April-2026</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1749,87 +1749,87 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>01-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>29-April-2026</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>28-April-2026</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1895,87 +1895,87 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>01-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>masterdata-hin</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>masterdata-hin</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>29-April-2026</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>masterdata-hin</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>28-April-2026</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -2041,112 +2041,112 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>01-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>masterdata-kan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>masterdata-kan</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>masterdata-kan</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>928</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>28-April-2026</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>masterdata-kan</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -2187,87 +2187,87 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>01-May-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>masterdata-tam</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>masterdata-tam</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>29-April-2026</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>masterdata-tam</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>28-April-2026</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -2333,87 +2333,87 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>01-May-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>312</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>29-April-2026</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>mimoto</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>349</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>312</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>28-April-2026</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -2479,112 +2479,112 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>01-May-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>32</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>28-April-2026</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>346</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>35</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2625,87 +2625,87 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>01-May-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>29-April-2026</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>28-April-2026</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
@@ -2771,107 +2771,107 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>01-May-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1140</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
         <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>28-April-2026</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>1131</t>
-        </is>
-      </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -2917,112 +2917,112 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>01-May-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>201</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
         <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>202</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>28-April-2026</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -3063,87 +3063,87 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>01-May-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>adminui</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>adminui</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
         <is>
           <t>29-April-2026</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>adminui</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>28-April-2026</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">

--- a/minio-report-tracker/xlxs/released.xlsx
+++ b/minio-report-tracker/xlxs/released.xlsx
@@ -811,13 +811,13 @@
     <col width="4" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
-    <col width="5" customWidth="1" min="12" max="12"/>
-    <col width="5" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
     <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="5" customWidth="1" min="15" max="15"/>
-    <col width="5" customWidth="1" min="16" max="16"/>
-    <col width="5" customWidth="1" min="17" max="17"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -905,1007 +905,1231 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>01-May-2026</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adminui</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v/>
-      </c>
-      <c r="K3" t="n">
-        <v/>
-      </c>
-      <c r="L3" t="n">
-        <v/>
-      </c>
-      <c r="M3" t="n">
-        <v/>
-      </c>
-      <c r="N3" t="n">
-        <v/>
-      </c>
-      <c r="O3" t="n">
-        <v/>
-      </c>
-      <c r="P3" t="n">
-        <v/>
-      </c>
-      <c r="Q3" t="n">
-        <v/>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v/>
-      </c>
-      <c r="K4" t="n">
-        <v/>
-      </c>
-      <c r="L4" t="n">
-        <v/>
-      </c>
-      <c r="M4" t="n">
-        <v/>
-      </c>
-      <c r="N4" t="n">
-        <v/>
-      </c>
-      <c r="O4" t="n">
-        <v/>
-      </c>
-      <c r="P4" t="n">
-        <v/>
-      </c>
-      <c r="Q4" t="n">
-        <v/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v/>
-      </c>
-      <c r="K5" t="n">
-        <v/>
-      </c>
-      <c r="L5" t="n">
-        <v/>
-      </c>
-      <c r="M5" t="n">
-        <v/>
-      </c>
-      <c r="N5" t="n">
-        <v/>
-      </c>
-      <c r="O5" t="n">
-        <v/>
-      </c>
-      <c r="P5" t="n">
-        <v/>
-      </c>
-      <c r="Q5" t="n">
-        <v/>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>943</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v/>
-      </c>
-      <c r="K6" t="n">
-        <v/>
-      </c>
-      <c r="L6" t="n">
-        <v/>
-      </c>
-      <c r="M6" t="n">
-        <v/>
-      </c>
-      <c r="N6" t="n">
-        <v/>
-      </c>
-      <c r="O6" t="n">
-        <v/>
-      </c>
-      <c r="P6" t="n">
-        <v/>
-      </c>
-      <c r="Q6" t="n">
-        <v/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v/>
-      </c>
-      <c r="K7" t="n">
-        <v/>
-      </c>
-      <c r="L7" t="n">
-        <v/>
-      </c>
-      <c r="M7" t="n">
-        <v/>
-      </c>
-      <c r="N7" t="n">
-        <v/>
-      </c>
-      <c r="O7" t="n">
-        <v/>
-      </c>
-      <c r="P7" t="n">
-        <v/>
-      </c>
-      <c r="Q7" t="n">
-        <v/>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>masterdata-hin</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>masterdata-hin</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v/>
-      </c>
-      <c r="K8" t="n">
-        <v/>
-      </c>
-      <c r="L8" t="n">
-        <v/>
-      </c>
-      <c r="M8" t="n">
-        <v/>
-      </c>
-      <c r="N8" t="n">
-        <v/>
-      </c>
-      <c r="O8" t="n">
-        <v/>
-      </c>
-      <c r="P8" t="n">
-        <v/>
-      </c>
-      <c r="Q8" t="n">
-        <v/>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>masterdata-kan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>masterdata-kan</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v/>
-      </c>
-      <c r="K9" t="n">
-        <v/>
-      </c>
-      <c r="L9" t="n">
-        <v/>
-      </c>
-      <c r="M9" t="n">
-        <v/>
-      </c>
-      <c r="N9" t="n">
-        <v/>
-      </c>
-      <c r="O9" t="n">
-        <v/>
-      </c>
-      <c r="P9" t="n">
-        <v/>
-      </c>
-      <c r="Q9" t="n">
-        <v/>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>masterdata-tam</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>masterdata-tam</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v/>
-      </c>
-      <c r="K10" t="n">
-        <v/>
-      </c>
-      <c r="L10" t="n">
-        <v/>
-      </c>
-      <c r="M10" t="n">
-        <v/>
-      </c>
-      <c r="N10" t="n">
-        <v/>
-      </c>
-      <c r="O10" t="n">
-        <v/>
-      </c>
-      <c r="P10" t="n">
-        <v/>
-      </c>
-      <c r="Q10" t="n">
-        <v/>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>357</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>320</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
-      </c>
-      <c r="J11" t="n">
-        <v/>
-      </c>
-      <c r="K11" t="n">
-        <v/>
-      </c>
-      <c r="L11" t="n">
-        <v/>
-      </c>
-      <c r="M11" t="n">
-        <v/>
-      </c>
-      <c r="N11" t="n">
-        <v/>
-      </c>
-      <c r="O11" t="n">
-        <v/>
-      </c>
-      <c r="P11" t="n">
-        <v/>
-      </c>
-      <c r="Q11" t="n">
-        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
-      </c>
-      <c r="J12" t="n">
-        <v/>
-      </c>
-      <c r="K12" t="n">
-        <v/>
-      </c>
-      <c r="L12" t="n">
-        <v/>
-      </c>
-      <c r="M12" t="n">
-        <v/>
-      </c>
-      <c r="N12" t="n">
-        <v/>
-      </c>
-      <c r="O12" t="n">
-        <v/>
-      </c>
-      <c r="P12" t="n">
-        <v/>
-      </c>
-      <c r="Q12" t="n">
-        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
-      </c>
-      <c r="J13" t="n">
-        <v/>
-      </c>
-      <c r="K13" t="n">
-        <v/>
-      </c>
-      <c r="L13" t="n">
-        <v/>
-      </c>
-      <c r="M13" t="n">
-        <v/>
-      </c>
-      <c r="N13" t="n">
-        <v/>
-      </c>
-      <c r="O13" t="n">
-        <v/>
-      </c>
-      <c r="P13" t="n">
-        <v/>
-      </c>
-      <c r="Q13" t="n">
-        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>1140</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v/>
-      </c>
-      <c r="K14" t="n">
-        <v/>
-      </c>
-      <c r="L14" t="n">
-        <v/>
-      </c>
-      <c r="M14" t="n">
-        <v/>
-      </c>
-      <c r="N14" t="n">
-        <v/>
-      </c>
-      <c r="O14" t="n">
-        <v/>
-      </c>
-      <c r="P14" t="n">
-        <v/>
-      </c>
-      <c r="Q14" t="n">
-        <v/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>197</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v/>
-      </c>
-      <c r="K15" t="n">
-        <v/>
-      </c>
-      <c r="L15" t="n">
-        <v/>
-      </c>
-      <c r="M15" t="n">
-        <v/>
-      </c>
-      <c r="N15" t="n">
-        <v/>
-      </c>
-      <c r="O15" t="n">
-        <v/>
-      </c>
-      <c r="P15" t="n">
-        <v/>
-      </c>
-      <c r="Q15" t="n">
-        <v/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>adminui</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>adminui</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v/>
-      </c>
-      <c r="K16" t="n">
-        <v/>
-      </c>
-      <c r="L16" t="n">
-        <v/>
-      </c>
-      <c r="M16" t="n">
-        <v/>
-      </c>
-      <c r="N16" t="n">
-        <v/>
-      </c>
-      <c r="O16" t="n">
-        <v/>
-      </c>
-      <c r="P16" t="n">
-        <v/>
-      </c>
-      <c r="Q16" t="n">
-        <v/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/released.xlsx
+++ b/minio-report-tracker/xlxs/released.xlsx
@@ -798,7 +798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:Z16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -806,9 +806,9 @@
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="4" customWidth="1" min="6" max="6"/>
-    <col width="4" customWidth="1" min="7" max="7"/>
-    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
@@ -818,6 +818,15 @@
     <col width="4" customWidth="1" min="15" max="15"/>
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="2" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
+    <col width="5" customWidth="1" min="23" max="23"/>
+    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -901,84 +910,164 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -987,80 +1076,120 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1069,80 +1198,120 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1151,80 +1320,120 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1233,80 +1442,120 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>943</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>943</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1315,80 +1564,120 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1397,80 +1686,120 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>masterdata-hin</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>masterdata-hin</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>masterdata-hin</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1479,80 +1808,120 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>masterdata-kan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>masterdata-kan</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>masterdata-kan</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1561,80 +1930,120 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>masterdata-tam</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>928</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>masterdata-tam</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>masterdata-tam</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1643,80 +2052,120 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>357</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>320</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>357</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>320</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1725,80 +2174,120 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -1807,80 +2296,120 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1140</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1889,80 +2418,120 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>1140</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1971,162 +2540,226 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>adminui</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>197</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>197</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" t="n">
+        <v/>
+      </c>
+      <c r="B16" t="n">
+        <v/>
+      </c>
+      <c r="C16" t="n">
+        <v/>
+      </c>
+      <c r="D16" t="n">
+        <v/>
+      </c>
+      <c r="E16" t="n">
+        <v/>
+      </c>
+      <c r="F16" t="n">
+        <v/>
+      </c>
+      <c r="G16" t="n">
+        <v/>
+      </c>
+      <c r="H16" t="n">
+        <v/>
+      </c>
+      <c r="J16" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>adminui</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>adminui</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/minio-report-tracker/xlxs/released.xlsx
+++ b/minio-report-tracker/xlxs/released.xlsx
@@ -798,7 +798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z16"/>
+  <dimension ref="A1:AI16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -806,18 +806,18 @@
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
-    <col width="5" customWidth="1" min="7" max="7"/>
-    <col width="5" customWidth="1" min="8" max="8"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="6" customWidth="1" min="12" max="12"/>
     <col width="6" customWidth="1" min="13" max="13"/>
     <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="4" customWidth="1" min="15" max="15"/>
-    <col width="4" customWidth="1" min="16" max="16"/>
-    <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="5" customWidth="1" min="15" max="15"/>
+    <col width="5" customWidth="1" min="16" max="16"/>
+    <col width="5" customWidth="1" min="17" max="17"/>
     <col width="2" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
     <col width="16" customWidth="1" min="20" max="20"/>
@@ -827,6 +827,15 @@
     <col width="4" customWidth="1" min="24" max="24"/>
     <col width="4" customWidth="1" min="25" max="25"/>
     <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="2" customWidth="1" min="27" max="27"/>
+    <col width="13" customWidth="1" min="28" max="28"/>
+    <col width="9" customWidth="1" min="29" max="29"/>
+    <col width="5" customWidth="1" min="30" max="30"/>
+    <col width="5" customWidth="1" min="31" max="31"/>
+    <col width="5" customWidth="1" min="32" max="32"/>
+    <col width="5" customWidth="1" min="33" max="33"/>
+    <col width="5" customWidth="1" min="34" max="34"/>
+    <col width="5" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -950,362 +959,466 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>9</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>adminui</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>04-May-2026</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
       <c r="Z3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB3" t="n">
+        <v/>
+      </c>
+      <c r="AC3" t="n">
+        <v/>
+      </c>
+      <c r="AD3" t="n">
+        <v/>
+      </c>
+      <c r="AE3" t="n">
+        <v/>
+      </c>
+      <c r="AF3" t="n">
+        <v/>
+      </c>
+      <c r="AG3" t="n">
+        <v/>
+      </c>
+      <c r="AH3" t="n">
+        <v/>
+      </c>
+      <c r="AI3" t="n">
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>04-May-2026</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>injiverify</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="Y4" t="inlineStr">
         <is>
           <t>0</t>
@@ -1315,241 +1428,289 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB4" t="n">
+        <v/>
+      </c>
+      <c r="AC4" t="n">
+        <v/>
+      </c>
+      <c r="AD4" t="n">
+        <v/>
+      </c>
+      <c r="AE4" t="n">
+        <v/>
+      </c>
+      <c r="AF4" t="n">
+        <v/>
+      </c>
+      <c r="AG4" t="n">
+        <v/>
+      </c>
+      <c r="AH4" t="n">
+        <v/>
+      </c>
+      <c r="AI4" t="n">
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>04-May-2026</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="Z5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB5" t="n">
+        <v/>
+      </c>
+      <c r="AC5" t="n">
+        <v/>
+      </c>
+      <c r="AD5" t="n">
+        <v/>
+      </c>
+      <c r="AE5" t="n">
+        <v/>
+      </c>
+      <c r="AF5" t="n">
+        <v/>
+      </c>
+      <c r="AG5" t="n">
+        <v/>
+      </c>
+      <c r="AH5" t="n">
+        <v/>
+      </c>
+      <c r="AI5" t="n">
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>943</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>943</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>04-May-2026</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="Y6" t="inlineStr">
         <is>
           <t>0</t>
@@ -1559,973 +1720,1165 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB6" t="n">
+        <v/>
+      </c>
+      <c r="AC6" t="n">
+        <v/>
+      </c>
+      <c r="AD6" t="n">
+        <v/>
+      </c>
+      <c r="AE6" t="n">
+        <v/>
+      </c>
+      <c r="AF6" t="n">
+        <v/>
+      </c>
+      <c r="AG6" t="n">
+        <v/>
+      </c>
+      <c r="AH6" t="n">
+        <v/>
+      </c>
+      <c r="AI6" t="n">
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>04-May-2026</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="Z7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB7" t="n">
+        <v/>
+      </c>
+      <c r="AC7" t="n">
+        <v/>
+      </c>
+      <c r="AD7" t="n">
+        <v/>
+      </c>
+      <c r="AE7" t="n">
+        <v/>
+      </c>
+      <c r="AF7" t="n">
+        <v/>
+      </c>
+      <c r="AG7" t="n">
+        <v/>
+      </c>
+      <c r="AH7" t="n">
+        <v/>
+      </c>
+      <c r="AI7" t="n">
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>masterdata-hin</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>928</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>masterdata-hin</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>masterdata-hin</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>04-May-2026</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>masterdata-hin</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="Z8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB8" t="n">
+        <v/>
+      </c>
+      <c r="AC8" t="n">
+        <v/>
+      </c>
+      <c r="AD8" t="n">
+        <v/>
+      </c>
+      <c r="AE8" t="n">
+        <v/>
+      </c>
+      <c r="AF8" t="n">
+        <v/>
+      </c>
+      <c r="AG8" t="n">
+        <v/>
+      </c>
+      <c r="AH8" t="n">
+        <v/>
+      </c>
+      <c r="AI8" t="n">
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>masterdata-kan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>masterdata-kan</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>masterdata-kan</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>04-May-2026</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>masterdata-kan</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="Z9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB9" t="n">
+        <v/>
+      </c>
+      <c r="AC9" t="n">
+        <v/>
+      </c>
+      <c r="AD9" t="n">
+        <v/>
+      </c>
+      <c r="AE9" t="n">
+        <v/>
+      </c>
+      <c r="AF9" t="n">
+        <v/>
+      </c>
+      <c r="AG9" t="n">
+        <v/>
+      </c>
+      <c r="AH9" t="n">
+        <v/>
+      </c>
+      <c r="AI9" t="n">
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>masterdata-tam</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>masterdata-tam</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>928</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>masterdata-tam</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>04-May-2026</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>masterdata-tam</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="Z10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB10" t="n">
+        <v/>
+      </c>
+      <c r="AC10" t="n">
+        <v/>
+      </c>
+      <c r="AD10" t="n">
+        <v/>
+      </c>
+      <c r="AE10" t="n">
+        <v/>
+      </c>
+      <c r="AF10" t="n">
+        <v/>
+      </c>
+      <c r="AG10" t="n">
+        <v/>
+      </c>
+      <c r="AH10" t="n">
+        <v/>
+      </c>
+      <c r="AI10" t="n">
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>357</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>320</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>04-May-2026</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>mimoto</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>357</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AB11" t="n">
+        <v/>
+      </c>
+      <c r="AC11" t="n">
+        <v/>
+      </c>
+      <c r="AD11" t="n">
+        <v/>
+      </c>
+      <c r="AE11" t="n">
+        <v/>
+      </c>
+      <c r="AF11" t="n">
+        <v/>
+      </c>
+      <c r="AG11" t="n">
+        <v/>
+      </c>
+      <c r="AH11" t="n">
+        <v/>
+      </c>
+      <c r="AI11" t="n">
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>04-May-2026</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>349</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="AB12" t="n">
+        <v/>
+      </c>
+      <c r="AC12" t="n">
+        <v/>
+      </c>
+      <c r="AD12" t="n">
+        <v/>
+      </c>
+      <c r="AE12" t="n">
+        <v/>
+      </c>
+      <c r="AF12" t="n">
+        <v/>
+      </c>
+      <c r="AG12" t="n">
+        <v/>
+      </c>
+      <c r="AH12" t="n">
+        <v/>
+      </c>
+      <c r="AI12" t="n">
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>1140</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>04-May-2026</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AB13" t="n">
+        <v/>
+      </c>
+      <c r="AC13" t="n">
+        <v/>
+      </c>
+      <c r="AD13" t="n">
+        <v/>
+      </c>
+      <c r="AE13" t="n">
+        <v/>
+      </c>
+      <c r="AF13" t="n">
+        <v/>
+      </c>
+      <c r="AG13" t="n">
+        <v/>
+      </c>
+      <c r="AH13" t="n">
+        <v/>
+      </c>
+      <c r="AI13" t="n">
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1135</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>197</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>04-May-2026</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>1140</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="Y14" t="inlineStr">
         <is>
           <t>0</t>
@@ -2535,119 +2888,143 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB14" t="n">
+        <v/>
+      </c>
+      <c r="AC14" t="n">
+        <v/>
+      </c>
+      <c r="AD14" t="n">
+        <v/>
+      </c>
+      <c r="AE14" t="n">
+        <v/>
+      </c>
+      <c r="AF14" t="n">
+        <v/>
+      </c>
+      <c r="AG14" t="n">
+        <v/>
+      </c>
+      <c r="AH14" t="n">
+        <v/>
+      </c>
+      <c r="AI14" t="n">
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>adminui</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>197</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>04-May-2026</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="Y15" t="inlineStr">
         <is>
           <t>0</t>
@@ -2657,103 +3034,127 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB15" t="n">
+        <v/>
+      </c>
+      <c r="AC15" t="n">
+        <v/>
+      </c>
+      <c r="AD15" t="n">
+        <v/>
+      </c>
+      <c r="AE15" t="n">
+        <v/>
+      </c>
+      <c r="AF15" t="n">
+        <v/>
+      </c>
+      <c r="AG15" t="n">
+        <v/>
+      </c>
+      <c r="AH15" t="n">
+        <v/>
+      </c>
+      <c r="AI15" t="n">
+        <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v/>
-      </c>
-      <c r="B16" t="n">
-        <v/>
-      </c>
-      <c r="C16" t="n">
-        <v/>
-      </c>
-      <c r="D16" t="n">
-        <v/>
-      </c>
-      <c r="E16" t="n">
-        <v/>
-      </c>
-      <c r="F16" t="n">
-        <v/>
-      </c>
-      <c r="G16" t="n">
-        <v/>
-      </c>
-      <c r="H16" t="n">
-        <v/>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>adminui</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v/>
+      </c>
+      <c r="K16" t="n">
+        <v/>
+      </c>
+      <c r="L16" t="n">
+        <v/>
+      </c>
+      <c r="M16" t="n">
+        <v/>
+      </c>
+      <c r="N16" t="n">
+        <v/>
+      </c>
+      <c r="O16" t="n">
+        <v/>
+      </c>
+      <c r="P16" t="n">
+        <v/>
+      </c>
+      <c r="Q16" t="n">
+        <v/>
+      </c>
+      <c r="S16" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>adminui</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>04-May-2026</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>adminui</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="Y16" t="inlineStr">
         <is>
           <t>0</t>
@@ -2763,6 +3164,30 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB16" t="n">
+        <v/>
+      </c>
+      <c r="AC16" t="n">
+        <v/>
+      </c>
+      <c r="AD16" t="n">
+        <v/>
+      </c>
+      <c r="AE16" t="n">
+        <v/>
+      </c>
+      <c r="AF16" t="n">
+        <v/>
+      </c>
+      <c r="AG16" t="n">
+        <v/>
+      </c>
+      <c r="AH16" t="n">
+        <v/>
+      </c>
+      <c r="AI16" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/released.xlsx
+++ b/minio-report-tracker/xlxs/released.xlsx
@@ -815,18 +815,18 @@
     <col width="6" customWidth="1" min="12" max="12"/>
     <col width="6" customWidth="1" min="13" max="13"/>
     <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="5" customWidth="1" min="15" max="15"/>
-    <col width="5" customWidth="1" min="16" max="16"/>
-    <col width="5" customWidth="1" min="17" max="17"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
     <col width="2" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
     <col width="16" customWidth="1" min="20" max="20"/>
     <col width="6" customWidth="1" min="21" max="21"/>
     <col width="6" customWidth="1" min="22" max="22"/>
     <col width="5" customWidth="1" min="23" max="23"/>
-    <col width="4" customWidth="1" min="24" max="24"/>
-    <col width="4" customWidth="1" min="25" max="25"/>
-    <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="5" customWidth="1" min="24" max="24"/>
+    <col width="5" customWidth="1" min="25" max="25"/>
+    <col width="5" customWidth="1" min="26" max="26"/>
     <col width="2" customWidth="1" min="27" max="27"/>
     <col width="13" customWidth="1" min="28" max="28"/>
     <col width="9" customWidth="1" min="29" max="29"/>
@@ -1003,127 +1003,127 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>08-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>05-May-2026</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>04-May-2026</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1165,87 +1165,87 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>08-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>06-May-2026</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>05-May-2026</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1311,87 +1311,87 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>08-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>06-May-2026</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>injiverify</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>05-May-2026</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1457,87 +1457,87 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>08-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>06-May-2026</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>05-May-2026</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1603,87 +1603,87 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>08-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>06-May-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>943</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>05-May-2026</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1749,87 +1749,87 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>08-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>06-May-2026</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>05-May-2026</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1895,87 +1895,87 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>08-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>masterdata-hin</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>masterdata-hin</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>928</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>06-May-2026</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>masterdata-hin</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>05-May-2026</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -2041,87 +2041,87 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>08-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>masterdata-kan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>masterdata-kan</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>06-May-2026</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>masterdata-kan</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>05-May-2026</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -2187,112 +2187,112 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>08-May-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>masterdata-tam</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>masterdata-tam</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>masterdata-tam</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>928</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>05-May-2026</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>masterdata-tam</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -2333,122 +2333,122 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>08-May-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>357</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>320</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>05-May-2026</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>mimoto</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>357</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="AB11" t="n">
@@ -2479,122 +2479,122 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>08-May-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>05-May-2026</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>349</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="AB12" t="n">
@@ -2625,122 +2625,122 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>08-May-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>1140</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>05-May-2026</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB13" t="n">
@@ -2771,112 +2771,112 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>08-May-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1140</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>1135</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
         <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>197</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>05-May-2026</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>1141</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2917,112 +2917,112 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>08-May-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>197</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
         <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>adminui</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>05-May-2026</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -3063,107 +3063,107 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>08-May-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>adminui</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>adminui</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v/>
-      </c>
-      <c r="K16" t="n">
-        <v/>
-      </c>
-      <c r="L16" t="n">
-        <v/>
-      </c>
-      <c r="M16" t="n">
-        <v/>
-      </c>
-      <c r="N16" t="n">
-        <v/>
-      </c>
-      <c r="O16" t="n">
-        <v/>
-      </c>
-      <c r="P16" t="n">
-        <v/>
-      </c>
-      <c r="Q16" t="n">
-        <v/>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>05-May-2026</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>adminui</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S16" t="n">
+        <v/>
+      </c>
+      <c r="T16" t="n">
+        <v/>
+      </c>
+      <c r="U16" t="n">
+        <v/>
+      </c>
+      <c r="V16" t="n">
+        <v/>
+      </c>
+      <c r="W16" t="n">
+        <v/>
+      </c>
+      <c r="X16" t="n">
+        <v/>
+      </c>
+      <c r="Y16" t="n">
+        <v/>
+      </c>
+      <c r="Z16" t="n">
+        <v/>
       </c>
       <c r="AB16" t="n">
         <v/>

--- a/minio-report-tracker/xlxs/released.xlsx
+++ b/minio-report-tracker/xlxs/released.xlsx
@@ -811,13 +811,13 @@
     <col width="4" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
-    <col width="5" customWidth="1" min="12" max="12"/>
-    <col width="5" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
     <col width="5" customWidth="1" min="14" max="14"/>
     <col width="5" customWidth="1" min="15" max="15"/>
-    <col width="5" customWidth="1" min="16" max="16"/>
-    <col width="5" customWidth="1" min="17" max="17"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -905,1007 +905,1231 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>08-May-2026</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adminui</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v/>
-      </c>
-      <c r="K3" t="n">
-        <v/>
-      </c>
-      <c r="L3" t="n">
-        <v/>
-      </c>
-      <c r="M3" t="n">
-        <v/>
-      </c>
-      <c r="N3" t="n">
-        <v/>
-      </c>
-      <c r="O3" t="n">
-        <v/>
-      </c>
-      <c r="P3" t="n">
-        <v/>
-      </c>
-      <c r="Q3" t="n">
-        <v/>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v/>
-      </c>
-      <c r="K4" t="n">
-        <v/>
-      </c>
-      <c r="L4" t="n">
-        <v/>
-      </c>
-      <c r="M4" t="n">
-        <v/>
-      </c>
-      <c r="N4" t="n">
-        <v/>
-      </c>
-      <c r="O4" t="n">
-        <v/>
-      </c>
-      <c r="P4" t="n">
-        <v/>
-      </c>
-      <c r="Q4" t="n">
-        <v/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v/>
-      </c>
-      <c r="K5" t="n">
-        <v/>
-      </c>
-      <c r="L5" t="n">
-        <v/>
-      </c>
-      <c r="M5" t="n">
-        <v/>
-      </c>
-      <c r="N5" t="n">
-        <v/>
-      </c>
-      <c r="O5" t="n">
-        <v/>
-      </c>
-      <c r="P5" t="n">
-        <v/>
-      </c>
-      <c r="Q5" t="n">
-        <v/>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v/>
-      </c>
-      <c r="K6" t="n">
-        <v/>
-      </c>
-      <c r="L6" t="n">
-        <v/>
-      </c>
-      <c r="M6" t="n">
-        <v/>
-      </c>
-      <c r="N6" t="n">
-        <v/>
-      </c>
-      <c r="O6" t="n">
-        <v/>
-      </c>
-      <c r="P6" t="n">
-        <v/>
-      </c>
-      <c r="Q6" t="n">
-        <v/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v/>
-      </c>
-      <c r="K7" t="n">
-        <v/>
-      </c>
-      <c r="L7" t="n">
-        <v/>
-      </c>
-      <c r="M7" t="n">
-        <v/>
-      </c>
-      <c r="N7" t="n">
-        <v/>
-      </c>
-      <c r="O7" t="n">
-        <v/>
-      </c>
-      <c r="P7" t="n">
-        <v/>
-      </c>
-      <c r="Q7" t="n">
-        <v/>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>masterdata-hin</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>masterdata-hin</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v/>
-      </c>
-      <c r="K8" t="n">
-        <v/>
-      </c>
-      <c r="L8" t="n">
-        <v/>
-      </c>
-      <c r="M8" t="n">
-        <v/>
-      </c>
-      <c r="N8" t="n">
-        <v/>
-      </c>
-      <c r="O8" t="n">
-        <v/>
-      </c>
-      <c r="P8" t="n">
-        <v/>
-      </c>
-      <c r="Q8" t="n">
-        <v/>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>masterdata-kan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>928</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>masterdata-kan</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v/>
-      </c>
-      <c r="K9" t="n">
-        <v/>
-      </c>
-      <c r="L9" t="n">
-        <v/>
-      </c>
-      <c r="M9" t="n">
-        <v/>
-      </c>
-      <c r="N9" t="n">
-        <v/>
-      </c>
-      <c r="O9" t="n">
-        <v/>
-      </c>
-      <c r="P9" t="n">
-        <v/>
-      </c>
-      <c r="Q9" t="n">
-        <v/>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>masterdata-tam</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>masterdata-tam</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v/>
-      </c>
-      <c r="K10" t="n">
-        <v/>
-      </c>
-      <c r="L10" t="n">
-        <v/>
-      </c>
-      <c r="M10" t="n">
-        <v/>
-      </c>
-      <c r="N10" t="n">
-        <v/>
-      </c>
-      <c r="O10" t="n">
-        <v/>
-      </c>
-      <c r="P10" t="n">
-        <v/>
-      </c>
-      <c r="Q10" t="n">
-        <v/>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>357</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>320</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
-      </c>
-      <c r="J11" t="n">
-        <v/>
-      </c>
-      <c r="K11" t="n">
-        <v/>
-      </c>
-      <c r="L11" t="n">
-        <v/>
-      </c>
-      <c r="M11" t="n">
-        <v/>
-      </c>
-      <c r="N11" t="n">
-        <v/>
-      </c>
-      <c r="O11" t="n">
-        <v/>
-      </c>
-      <c r="P11" t="n">
-        <v/>
-      </c>
-      <c r="Q11" t="n">
-        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
-      </c>
-      <c r="J12" t="n">
-        <v/>
-      </c>
-      <c r="K12" t="n">
-        <v/>
-      </c>
-      <c r="L12" t="n">
-        <v/>
-      </c>
-      <c r="M12" t="n">
-        <v/>
-      </c>
-      <c r="N12" t="n">
-        <v/>
-      </c>
-      <c r="O12" t="n">
-        <v/>
-      </c>
-      <c r="P12" t="n">
-        <v/>
-      </c>
-      <c r="Q12" t="n">
-        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
-      </c>
-      <c r="J13" t="n">
-        <v/>
-      </c>
-      <c r="K13" t="n">
-        <v/>
-      </c>
-      <c r="L13" t="n">
-        <v/>
-      </c>
-      <c r="M13" t="n">
-        <v/>
-      </c>
-      <c r="N13" t="n">
-        <v/>
-      </c>
-      <c r="O13" t="n">
-        <v/>
-      </c>
-      <c r="P13" t="n">
-        <v/>
-      </c>
-      <c r="Q13" t="n">
-        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v/>
-      </c>
-      <c r="K14" t="n">
-        <v/>
-      </c>
-      <c r="L14" t="n">
-        <v/>
-      </c>
-      <c r="M14" t="n">
-        <v/>
-      </c>
-      <c r="N14" t="n">
-        <v/>
-      </c>
-      <c r="O14" t="n">
-        <v/>
-      </c>
-      <c r="P14" t="n">
-        <v/>
-      </c>
-      <c r="Q14" t="n">
-        <v/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v/>
-      </c>
-      <c r="K15" t="n">
-        <v/>
-      </c>
-      <c r="L15" t="n">
-        <v/>
-      </c>
-      <c r="M15" t="n">
-        <v/>
-      </c>
-      <c r="N15" t="n">
-        <v/>
-      </c>
-      <c r="O15" t="n">
-        <v/>
-      </c>
-      <c r="P15" t="n">
-        <v/>
-      </c>
-      <c r="Q15" t="n">
-        <v/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>adminui</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>adminui</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v/>
-      </c>
-      <c r="K16" t="n">
-        <v/>
-      </c>
-      <c r="L16" t="n">
-        <v/>
-      </c>
-      <c r="M16" t="n">
-        <v/>
-      </c>
-      <c r="N16" t="n">
-        <v/>
-      </c>
-      <c r="O16" t="n">
-        <v/>
-      </c>
-      <c r="P16" t="n">
-        <v/>
-      </c>
-      <c r="Q16" t="n">
-        <v/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/released.xlsx
+++ b/minio-report-tracker/xlxs/released.xlsx
@@ -798,7 +798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:Z16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -818,6 +818,15 @@
     <col width="5" customWidth="1" min="15" max="15"/>
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="2" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
+    <col width="5" customWidth="1" min="23" max="23"/>
+    <col width="5" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -901,84 +910,164 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -987,80 +1076,120 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1069,80 +1198,120 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1151,80 +1320,120 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1233,80 +1442,120 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1315,80 +1564,120 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1397,80 +1686,120 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>masterdata-hin</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>masterdata-hin</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>masterdata-hin</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1479,80 +1808,120 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>masterdata-kan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>masterdata-kan</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>928</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>masterdata-kan</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1561,80 +1930,120 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>masterdata-tam</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>masterdata-tam</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>masterdata-tam</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1643,80 +2052,120 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>357</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>320</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>357</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>320</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1725,80 +2174,120 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -1807,80 +2296,120 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1889,80 +2418,120 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1052</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
         <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1971,80 +2540,120 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
         <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -2053,80 +2662,120 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>adminui</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>adminui</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
         <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>adminui</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/minio-report-tracker/xlxs/released.xlsx
+++ b/minio-report-tracker/xlxs/released.xlsx
@@ -798,7 +798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z16"/>
+  <dimension ref="A1:AI16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -827,6 +827,15 @@
     <col width="5" customWidth="1" min="24" max="24"/>
     <col width="4" customWidth="1" min="25" max="25"/>
     <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="2" customWidth="1" min="27" max="27"/>
+    <col width="13" customWidth="1" min="28" max="28"/>
+    <col width="9" customWidth="1" min="29" max="29"/>
+    <col width="5" customWidth="1" min="30" max="30"/>
+    <col width="5" customWidth="1" min="31" max="31"/>
+    <col width="5" customWidth="1" min="32" max="32"/>
+    <col width="5" customWidth="1" min="33" max="33"/>
+    <col width="5" customWidth="1" min="34" max="34"/>
+    <col width="5" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -950,246 +959,366 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>9</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>adminui</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1198,114 +1327,114 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>11-May-2026</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>injiverify</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="Y4" t="inlineStr">
         <is>
           <t>0</t>
@@ -1315,241 +1444,289 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB4" t="n">
+        <v/>
+      </c>
+      <c r="AC4" t="n">
+        <v/>
+      </c>
+      <c r="AD4" t="n">
+        <v/>
+      </c>
+      <c r="AE4" t="n">
+        <v/>
+      </c>
+      <c r="AF4" t="n">
+        <v/>
+      </c>
+      <c r="AG4" t="n">
+        <v/>
+      </c>
+      <c r="AH4" t="n">
+        <v/>
+      </c>
+      <c r="AI4" t="n">
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>11-May-2026</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="Z5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB5" t="n">
+        <v/>
+      </c>
+      <c r="AC5" t="n">
+        <v/>
+      </c>
+      <c r="AD5" t="n">
+        <v/>
+      </c>
+      <c r="AE5" t="n">
+        <v/>
+      </c>
+      <c r="AF5" t="n">
+        <v/>
+      </c>
+      <c r="AG5" t="n">
+        <v/>
+      </c>
+      <c r="AH5" t="n">
+        <v/>
+      </c>
+      <c r="AI5" t="n">
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>11-May-2026</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="Y6" t="inlineStr">
         <is>
           <t>0</t>
@@ -1559,973 +1736,1165 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB6" t="n">
+        <v/>
+      </c>
+      <c r="AC6" t="n">
+        <v/>
+      </c>
+      <c r="AD6" t="n">
+        <v/>
+      </c>
+      <c r="AE6" t="n">
+        <v/>
+      </c>
+      <c r="AF6" t="n">
+        <v/>
+      </c>
+      <c r="AG6" t="n">
+        <v/>
+      </c>
+      <c r="AH6" t="n">
+        <v/>
+      </c>
+      <c r="AI6" t="n">
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>11-May-2026</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="Z7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB7" t="n">
+        <v/>
+      </c>
+      <c r="AC7" t="n">
+        <v/>
+      </c>
+      <c r="AD7" t="n">
+        <v/>
+      </c>
+      <c r="AE7" t="n">
+        <v/>
+      </c>
+      <c r="AF7" t="n">
+        <v/>
+      </c>
+      <c r="AG7" t="n">
+        <v/>
+      </c>
+      <c r="AH7" t="n">
+        <v/>
+      </c>
+      <c r="AI7" t="n">
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>masterdata-hin</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>masterdata-hin</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>masterdata-hin</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>11-May-2026</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>masterdata-hin</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="Z8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB8" t="n">
+        <v/>
+      </c>
+      <c r="AC8" t="n">
+        <v/>
+      </c>
+      <c r="AD8" t="n">
+        <v/>
+      </c>
+      <c r="AE8" t="n">
+        <v/>
+      </c>
+      <c r="AF8" t="n">
+        <v/>
+      </c>
+      <c r="AG8" t="n">
+        <v/>
+      </c>
+      <c r="AH8" t="n">
+        <v/>
+      </c>
+      <c r="AI8" t="n">
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>masterdata-kan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>masterdata-kan</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>masterdata-kan</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>928</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>11-May-2026</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>masterdata-kan</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="Z9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB9" t="n">
+        <v/>
+      </c>
+      <c r="AC9" t="n">
+        <v/>
+      </c>
+      <c r="AD9" t="n">
+        <v/>
+      </c>
+      <c r="AE9" t="n">
+        <v/>
+      </c>
+      <c r="AF9" t="n">
+        <v/>
+      </c>
+      <c r="AG9" t="n">
+        <v/>
+      </c>
+      <c r="AH9" t="n">
+        <v/>
+      </c>
+      <c r="AI9" t="n">
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>masterdata-tam</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>masterdata-tam</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>masterdata-tam</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>11-May-2026</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>masterdata-tam</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="Z10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB10" t="n">
+        <v/>
+      </c>
+      <c r="AC10" t="n">
+        <v/>
+      </c>
+      <c r="AD10" t="n">
+        <v/>
+      </c>
+      <c r="AE10" t="n">
+        <v/>
+      </c>
+      <c r="AF10" t="n">
+        <v/>
+      </c>
+      <c r="AG10" t="n">
+        <v/>
+      </c>
+      <c r="AH10" t="n">
+        <v/>
+      </c>
+      <c r="AI10" t="n">
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>357</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>320</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>357</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>320</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>11-May-2026</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>mimoto</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>357</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AB11" t="n">
+        <v/>
+      </c>
+      <c r="AC11" t="n">
+        <v/>
+      </c>
+      <c r="AD11" t="n">
+        <v/>
+      </c>
+      <c r="AE11" t="n">
+        <v/>
+      </c>
+      <c r="AF11" t="n">
+        <v/>
+      </c>
+      <c r="AG11" t="n">
+        <v/>
+      </c>
+      <c r="AH11" t="n">
+        <v/>
+      </c>
+      <c r="AI11" t="n">
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>11-May-2026</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>349</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="AB12" t="n">
+        <v/>
+      </c>
+      <c r="AC12" t="n">
+        <v/>
+      </c>
+      <c r="AD12" t="n">
+        <v/>
+      </c>
+      <c r="AE12" t="n">
+        <v/>
+      </c>
+      <c r="AF12" t="n">
+        <v/>
+      </c>
+      <c r="AG12" t="n">
+        <v/>
+      </c>
+      <c r="AH12" t="n">
+        <v/>
+      </c>
+      <c r="AI12" t="n">
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>11-May-2026</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AB13" t="n">
+        <v/>
+      </c>
+      <c r="AC13" t="n">
+        <v/>
+      </c>
+      <c r="AD13" t="n">
+        <v/>
+      </c>
+      <c r="AE13" t="n">
+        <v/>
+      </c>
+      <c r="AF13" t="n">
+        <v/>
+      </c>
+      <c r="AG13" t="n">
+        <v/>
+      </c>
+      <c r="AH13" t="n">
+        <v/>
+      </c>
+      <c r="AI13" t="n">
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1054</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>1052</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
         <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>11-May-2026</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>1141</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="Y14" t="inlineStr">
         <is>
           <t>0</t>
@@ -2535,119 +2904,143 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB14" t="n">
+        <v/>
+      </c>
+      <c r="AC14" t="n">
+        <v/>
+      </c>
+      <c r="AD14" t="n">
+        <v/>
+      </c>
+      <c r="AE14" t="n">
+        <v/>
+      </c>
+      <c r="AF14" t="n">
+        <v/>
+      </c>
+      <c r="AG14" t="n">
+        <v/>
+      </c>
+      <c r="AH14" t="n">
+        <v/>
+      </c>
+      <c r="AI14" t="n">
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
         <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>11-May-2026</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
       <c r="Y15" t="inlineStr">
         <is>
           <t>0</t>
@@ -2657,109 +3050,133 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB15" t="n">
+        <v/>
+      </c>
+      <c r="AC15" t="n">
+        <v/>
+      </c>
+      <c r="AD15" t="n">
+        <v/>
+      </c>
+      <c r="AE15" t="n">
+        <v/>
+      </c>
+      <c r="AF15" t="n">
+        <v/>
+      </c>
+      <c r="AG15" t="n">
+        <v/>
+      </c>
+      <c r="AH15" t="n">
+        <v/>
+      </c>
+      <c r="AI15" t="n">
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>adminui</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>adminui</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
         <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>adminui</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>11-May-2026</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>adminui</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="W16" t="inlineStr">
         <is>
           <t>0</t>
@@ -2767,7 +3184,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2779,6 +3196,30 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB16" t="n">
+        <v/>
+      </c>
+      <c r="AC16" t="n">
+        <v/>
+      </c>
+      <c r="AD16" t="n">
+        <v/>
+      </c>
+      <c r="AE16" t="n">
+        <v/>
+      </c>
+      <c r="AF16" t="n">
+        <v/>
+      </c>
+      <c r="AG16" t="n">
+        <v/>
+      </c>
+      <c r="AH16" t="n">
+        <v/>
+      </c>
+      <c r="AI16" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/released.xlsx
+++ b/minio-report-tracker/xlxs/released.xlsx
@@ -1003,152 +1003,152 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>597</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11-May-2026</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>dsl</t>
+          <t>adminui</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
@@ -1165,249 +1165,233 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>12-May-2026</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
       <c r="Z3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11-May-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>adminui</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AB3" t="n">
+        <v/>
+      </c>
+      <c r="AC3" t="n">
+        <v/>
+      </c>
+      <c r="AD3" t="n">
+        <v/>
+      </c>
+      <c r="AE3" t="n">
+        <v/>
+      </c>
+      <c r="AF3" t="n">
+        <v/>
+      </c>
+      <c r="AG3" t="n">
+        <v/>
+      </c>
+      <c r="AH3" t="n">
+        <v/>
+      </c>
+      <c r="AI3" t="n">
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>81</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>injiverify</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>12-May-2026</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1473,87 +1457,87 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>12-May-2026</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1619,87 +1603,87 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>12-May-2026</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1765,87 +1749,87 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>12-May-2026</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1911,87 +1895,87 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>masterdata-hin</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>masterdata-hin</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>masterdata-hin</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>12-May-2026</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -2057,112 +2041,112 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>masterdata-kan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>masterdata-kan</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>masterdata-kan</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>12-May-2026</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>masterdata-kan</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>928</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -2203,87 +2187,87 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>masterdata-tam</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>masterdata-tam</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>masterdata-tam</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>12-May-2026</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -2349,87 +2333,87 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>357</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>320</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>mimoto</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>357</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>12-May-2026</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -2495,112 +2479,112 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>32</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>12-May-2026</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>31</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2641,87 +2625,87 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>12-May-2026</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
@@ -2787,112 +2771,112 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1054</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>1054</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
         <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>1052</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
         <is>
           <t>90</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>12-May-2026</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>1141</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2933,112 +2917,112 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
         <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>100</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>12-May-2026</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>101</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -3079,112 +3063,112 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>adminui</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>adminui</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
         <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>adminui</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>12-May-2026</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>adminui</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">

--- a/minio-report-tracker/xlxs/released.xlsx
+++ b/minio-report-tracker/xlxs/released.xlsx
@@ -811,13 +811,13 @@
     <col width="4" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="5" customWidth="1" min="12" max="12"/>
-    <col width="5" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
     <col width="5" customWidth="1" min="14" max="14"/>
     <col width="5" customWidth="1" min="15" max="15"/>
-    <col width="5" customWidth="1" min="16" max="16"/>
-    <col width="5" customWidth="1" min="17" max="17"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -905,159 +905,159 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>15-May-2026</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>injiverify</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>15-May-2026</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adminui</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -1069,859 +1069,1067 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>110</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v/>
-      </c>
-      <c r="K4" t="n">
-        <v/>
-      </c>
-      <c r="L4" t="n">
-        <v/>
-      </c>
-      <c r="M4" t="n">
-        <v/>
-      </c>
-      <c r="N4" t="n">
-        <v/>
-      </c>
-      <c r="O4" t="n">
-        <v/>
-      </c>
-      <c r="P4" t="n">
-        <v/>
-      </c>
-      <c r="Q4" t="n">
-        <v/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v/>
-      </c>
-      <c r="K5" t="n">
-        <v/>
-      </c>
-      <c r="L5" t="n">
-        <v/>
-      </c>
-      <c r="M5" t="n">
-        <v/>
-      </c>
-      <c r="N5" t="n">
-        <v/>
-      </c>
-      <c r="O5" t="n">
-        <v/>
-      </c>
-      <c r="P5" t="n">
-        <v/>
-      </c>
-      <c r="Q5" t="n">
-        <v/>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v/>
-      </c>
-      <c r="K6" t="n">
-        <v/>
-      </c>
-      <c r="L6" t="n">
-        <v/>
-      </c>
-      <c r="M6" t="n">
-        <v/>
-      </c>
-      <c r="N6" t="n">
-        <v/>
-      </c>
-      <c r="O6" t="n">
-        <v/>
-      </c>
-      <c r="P6" t="n">
-        <v/>
-      </c>
-      <c r="Q6" t="n">
-        <v/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v/>
-      </c>
-      <c r="K7" t="n">
-        <v/>
-      </c>
-      <c r="L7" t="n">
-        <v/>
-      </c>
-      <c r="M7" t="n">
-        <v/>
-      </c>
-      <c r="N7" t="n">
-        <v/>
-      </c>
-      <c r="O7" t="n">
-        <v/>
-      </c>
-      <c r="P7" t="n">
-        <v/>
-      </c>
-      <c r="Q7" t="n">
-        <v/>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>masterdata-hin</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>masterdata-hin</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v/>
-      </c>
-      <c r="K8" t="n">
-        <v/>
-      </c>
-      <c r="L8" t="n">
-        <v/>
-      </c>
-      <c r="M8" t="n">
-        <v/>
-      </c>
-      <c r="N8" t="n">
-        <v/>
-      </c>
-      <c r="O8" t="n">
-        <v/>
-      </c>
-      <c r="P8" t="n">
-        <v/>
-      </c>
-      <c r="Q8" t="n">
-        <v/>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>masterdata-kan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>masterdata-kan</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v/>
-      </c>
-      <c r="K9" t="n">
-        <v/>
-      </c>
-      <c r="L9" t="n">
-        <v/>
-      </c>
-      <c r="M9" t="n">
-        <v/>
-      </c>
-      <c r="N9" t="n">
-        <v/>
-      </c>
-      <c r="O9" t="n">
-        <v/>
-      </c>
-      <c r="P9" t="n">
-        <v/>
-      </c>
-      <c r="Q9" t="n">
-        <v/>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>masterdata-tam</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>masterdata-tam</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v/>
-      </c>
-      <c r="K10" t="n">
-        <v/>
-      </c>
-      <c r="L10" t="n">
-        <v/>
-      </c>
-      <c r="M10" t="n">
-        <v/>
-      </c>
-      <c r="N10" t="n">
-        <v/>
-      </c>
-      <c r="O10" t="n">
-        <v/>
-      </c>
-      <c r="P10" t="n">
-        <v/>
-      </c>
-      <c r="Q10" t="n">
-        <v/>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>357</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>320</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
-      </c>
-      <c r="J11" t="n">
-        <v/>
-      </c>
-      <c r="K11" t="n">
-        <v/>
-      </c>
-      <c r="L11" t="n">
-        <v/>
-      </c>
-      <c r="M11" t="n">
-        <v/>
-      </c>
-      <c r="N11" t="n">
-        <v/>
-      </c>
-      <c r="O11" t="n">
-        <v/>
-      </c>
-      <c r="P11" t="n">
-        <v/>
-      </c>
-      <c r="Q11" t="n">
-        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
-      </c>
-      <c r="J12" t="n">
-        <v/>
-      </c>
-      <c r="K12" t="n">
-        <v/>
-      </c>
-      <c r="L12" t="n">
-        <v/>
-      </c>
-      <c r="M12" t="n">
-        <v/>
-      </c>
-      <c r="N12" t="n">
-        <v/>
-      </c>
-      <c r="O12" t="n">
-        <v/>
-      </c>
-      <c r="P12" t="n">
-        <v/>
-      </c>
-      <c r="Q12" t="n">
-        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
-      </c>
-      <c r="J13" t="n">
-        <v/>
-      </c>
-      <c r="K13" t="n">
-        <v/>
-      </c>
-      <c r="L13" t="n">
-        <v/>
-      </c>
-      <c r="M13" t="n">
-        <v/>
-      </c>
-      <c r="N13" t="n">
-        <v/>
-      </c>
-      <c r="O13" t="n">
-        <v/>
-      </c>
-      <c r="P13" t="n">
-        <v/>
-      </c>
-      <c r="Q13" t="n">
-        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1054</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>1051</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>91</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v/>
-      </c>
-      <c r="K14" t="n">
-        <v/>
-      </c>
-      <c r="L14" t="n">
-        <v/>
-      </c>
-      <c r="M14" t="n">
-        <v/>
-      </c>
-      <c r="N14" t="n">
-        <v/>
-      </c>
-      <c r="O14" t="n">
-        <v/>
-      </c>
-      <c r="P14" t="n">
-        <v/>
-      </c>
-      <c r="Q14" t="n">
-        <v/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v/>
-      </c>
-      <c r="K15" t="n">
-        <v/>
-      </c>
-      <c r="L15" t="n">
-        <v/>
-      </c>
-      <c r="M15" t="n">
-        <v/>
-      </c>
-      <c r="N15" t="n">
-        <v/>
-      </c>
-      <c r="O15" t="n">
-        <v/>
-      </c>
-      <c r="P15" t="n">
-        <v/>
-      </c>
-      <c r="Q15" t="n">
-        <v/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>adminui</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>adminui</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v/>
-      </c>
-      <c r="K16" t="n">
-        <v/>
-      </c>
-      <c r="L16" t="n">
-        <v/>
-      </c>
-      <c r="M16" t="n">
-        <v/>
-      </c>
-      <c r="N16" t="n">
-        <v/>
-      </c>
-      <c r="O16" t="n">
-        <v/>
-      </c>
-      <c r="P16" t="n">
-        <v/>
-      </c>
-      <c r="Q16" t="n">
-        <v/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/released.xlsx
+++ b/minio-report-tracker/xlxs/released.xlsx
@@ -798,7 +798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:Z16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -818,6 +818,15 @@
     <col width="5" customWidth="1" min="15" max="15"/>
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="2" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
+    <col width="5" customWidth="1" min="23" max="23"/>
+    <col width="5" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -901,84 +910,164 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -987,80 +1076,120 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1069,80 +1198,120 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>110</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>110</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1151,80 +1320,120 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>928</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1233,80 +1442,120 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1315,80 +1564,120 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1397,80 +1686,120 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>masterdata-hin</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>masterdata-hin</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>masterdata-hin</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1479,80 +1808,120 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>masterdata-kan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>masterdata-kan</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>masterdata-kan</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1561,80 +1930,120 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>masterdata-tam</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>masterdata-tam</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>masterdata-tam</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1643,80 +2052,120 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>357</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>320</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>357</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>320</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1725,80 +2174,120 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -1807,80 +2296,120 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1889,80 +2418,120 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1054</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>1054</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>1051</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
         <is>
           <t>91</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1971,80 +2540,120 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -2053,80 +2662,120 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>adminui</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>adminui</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>adminui</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/minio-report-tracker/xlxs/released.xlsx
+++ b/minio-report-tracker/xlxs/released.xlsx
@@ -798,7 +798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z16"/>
+  <dimension ref="A1:AI16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -827,6 +827,15 @@
     <col width="5" customWidth="1" min="24" max="24"/>
     <col width="4" customWidth="1" min="25" max="25"/>
     <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="2" customWidth="1" min="27" max="27"/>
+    <col width="13" customWidth="1" min="28" max="28"/>
+    <col width="9" customWidth="1" min="29" max="29"/>
+    <col width="5" customWidth="1" min="30" max="30"/>
+    <col width="5" customWidth="1" min="31" max="31"/>
+    <col width="5" customWidth="1" min="32" max="32"/>
+    <col width="5" customWidth="1" min="33" max="33"/>
+    <col width="5" customWidth="1" min="34" max="34"/>
+    <col width="5" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -950,362 +959,466 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>9</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>adminui</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
       <c r="Z3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB3" t="n">
+        <v/>
+      </c>
+      <c r="AC3" t="n">
+        <v/>
+      </c>
+      <c r="AD3" t="n">
+        <v/>
+      </c>
+      <c r="AE3" t="n">
+        <v/>
+      </c>
+      <c r="AF3" t="n">
+        <v/>
+      </c>
+      <c r="AG3" t="n">
+        <v/>
+      </c>
+      <c r="AH3" t="n">
+        <v/>
+      </c>
+      <c r="AI3" t="n">
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>110</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>110</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>injiverify</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="Y4" t="inlineStr">
         <is>
           <t>0</t>
@@ -1315,241 +1428,289 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB4" t="n">
+        <v/>
+      </c>
+      <c r="AC4" t="n">
+        <v/>
+      </c>
+      <c r="AD4" t="n">
+        <v/>
+      </c>
+      <c r="AE4" t="n">
+        <v/>
+      </c>
+      <c r="AF4" t="n">
+        <v/>
+      </c>
+      <c r="AG4" t="n">
+        <v/>
+      </c>
+      <c r="AH4" t="n">
+        <v/>
+      </c>
+      <c r="AI4" t="n">
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>928</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="Z5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB5" t="n">
+        <v/>
+      </c>
+      <c r="AC5" t="n">
+        <v/>
+      </c>
+      <c r="AD5" t="n">
+        <v/>
+      </c>
+      <c r="AE5" t="n">
+        <v/>
+      </c>
+      <c r="AF5" t="n">
+        <v/>
+      </c>
+      <c r="AG5" t="n">
+        <v/>
+      </c>
+      <c r="AH5" t="n">
+        <v/>
+      </c>
+      <c r="AI5" t="n">
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="Y6" t="inlineStr">
         <is>
           <t>0</t>
@@ -1559,973 +1720,1165 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB6" t="n">
+        <v/>
+      </c>
+      <c r="AC6" t="n">
+        <v/>
+      </c>
+      <c r="AD6" t="n">
+        <v/>
+      </c>
+      <c r="AE6" t="n">
+        <v/>
+      </c>
+      <c r="AF6" t="n">
+        <v/>
+      </c>
+      <c r="AG6" t="n">
+        <v/>
+      </c>
+      <c r="AH6" t="n">
+        <v/>
+      </c>
+      <c r="AI6" t="n">
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="Z7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB7" t="n">
+        <v/>
+      </c>
+      <c r="AC7" t="n">
+        <v/>
+      </c>
+      <c r="AD7" t="n">
+        <v/>
+      </c>
+      <c r="AE7" t="n">
+        <v/>
+      </c>
+      <c r="AF7" t="n">
+        <v/>
+      </c>
+      <c r="AG7" t="n">
+        <v/>
+      </c>
+      <c r="AH7" t="n">
+        <v/>
+      </c>
+      <c r="AI7" t="n">
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>masterdata-hin</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>masterdata-hin</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>masterdata-hin</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>masterdata-hin</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="Z8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB8" t="n">
+        <v/>
+      </c>
+      <c r="AC8" t="n">
+        <v/>
+      </c>
+      <c r="AD8" t="n">
+        <v/>
+      </c>
+      <c r="AE8" t="n">
+        <v/>
+      </c>
+      <c r="AF8" t="n">
+        <v/>
+      </c>
+      <c r="AG8" t="n">
+        <v/>
+      </c>
+      <c r="AH8" t="n">
+        <v/>
+      </c>
+      <c r="AI8" t="n">
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>masterdata-kan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>masterdata-kan</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>masterdata-kan</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>masterdata-kan</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="Z9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB9" t="n">
+        <v/>
+      </c>
+      <c r="AC9" t="n">
+        <v/>
+      </c>
+      <c r="AD9" t="n">
+        <v/>
+      </c>
+      <c r="AE9" t="n">
+        <v/>
+      </c>
+      <c r="AF9" t="n">
+        <v/>
+      </c>
+      <c r="AG9" t="n">
+        <v/>
+      </c>
+      <c r="AH9" t="n">
+        <v/>
+      </c>
+      <c r="AI9" t="n">
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>masterdata-tam</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>masterdata-tam</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>masterdata-tam</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>masterdata-tam</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="Z10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB10" t="n">
+        <v/>
+      </c>
+      <c r="AC10" t="n">
+        <v/>
+      </c>
+      <c r="AD10" t="n">
+        <v/>
+      </c>
+      <c r="AE10" t="n">
+        <v/>
+      </c>
+      <c r="AF10" t="n">
+        <v/>
+      </c>
+      <c r="AG10" t="n">
+        <v/>
+      </c>
+      <c r="AH10" t="n">
+        <v/>
+      </c>
+      <c r="AI10" t="n">
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>357</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>320</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>357</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>320</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>mimoto</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>357</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AB11" t="n">
+        <v/>
+      </c>
+      <c r="AC11" t="n">
+        <v/>
+      </c>
+      <c r="AD11" t="n">
+        <v/>
+      </c>
+      <c r="AE11" t="n">
+        <v/>
+      </c>
+      <c r="AF11" t="n">
+        <v/>
+      </c>
+      <c r="AG11" t="n">
+        <v/>
+      </c>
+      <c r="AH11" t="n">
+        <v/>
+      </c>
+      <c r="AI11" t="n">
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>349</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="AB12" t="n">
+        <v/>
+      </c>
+      <c r="AC12" t="n">
+        <v/>
+      </c>
+      <c r="AD12" t="n">
+        <v/>
+      </c>
+      <c r="AE12" t="n">
+        <v/>
+      </c>
+      <c r="AF12" t="n">
+        <v/>
+      </c>
+      <c r="AG12" t="n">
+        <v/>
+      </c>
+      <c r="AH12" t="n">
+        <v/>
+      </c>
+      <c r="AI12" t="n">
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AB13" t="n">
+        <v/>
+      </c>
+      <c r="AC13" t="n">
+        <v/>
+      </c>
+      <c r="AD13" t="n">
+        <v/>
+      </c>
+      <c r="AE13" t="n">
+        <v/>
+      </c>
+      <c r="AF13" t="n">
+        <v/>
+      </c>
+      <c r="AG13" t="n">
+        <v/>
+      </c>
+      <c r="AH13" t="n">
+        <v/>
+      </c>
+      <c r="AI13" t="n">
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1139</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>1054</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>1054</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>1051</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
       <c r="Y14" t="inlineStr">
         <is>
           <t>0</t>
@@ -2535,119 +2888,143 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB14" t="n">
+        <v/>
+      </c>
+      <c r="AC14" t="n">
+        <v/>
+      </c>
+      <c r="AD14" t="n">
+        <v/>
+      </c>
+      <c r="AE14" t="n">
+        <v/>
+      </c>
+      <c r="AF14" t="n">
+        <v/>
+      </c>
+      <c r="AG14" t="n">
+        <v/>
+      </c>
+      <c r="AH14" t="n">
+        <v/>
+      </c>
+      <c r="AI14" t="n">
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
       <c r="Y15" t="inlineStr">
         <is>
           <t>0</t>
@@ -2657,109 +3034,133 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB15" t="n">
+        <v/>
+      </c>
+      <c r="AC15" t="n">
+        <v/>
+      </c>
+      <c r="AD15" t="n">
+        <v/>
+      </c>
+      <c r="AE15" t="n">
+        <v/>
+      </c>
+      <c r="AF15" t="n">
+        <v/>
+      </c>
+      <c r="AG15" t="n">
+        <v/>
+      </c>
+      <c r="AH15" t="n">
+        <v/>
+      </c>
+      <c r="AI15" t="n">
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>adminui</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>adminui</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>adminui</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>adminui</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="W16" t="inlineStr">
         <is>
           <t>0</t>
@@ -2767,7 +3168,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2779,6 +3180,30 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+      <c r="AB16" t="n">
+        <v/>
+      </c>
+      <c r="AC16" t="n">
+        <v/>
+      </c>
+      <c r="AD16" t="n">
+        <v/>
+      </c>
+      <c r="AE16" t="n">
+        <v/>
+      </c>
+      <c r="AF16" t="n">
+        <v/>
+      </c>
+      <c r="AG16" t="n">
+        <v/>
+      </c>
+      <c r="AH16" t="n">
+        <v/>
+      </c>
+      <c r="AI16" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/released.xlsx
+++ b/minio-report-tracker/xlxs/released.xlsx
@@ -1003,129 +1003,129 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>22-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>597</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
           <t>adminui</t>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
@@ -1165,87 +1165,87 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>22-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>20-May-2026</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>19-May-2026</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1311,87 +1311,87 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>22-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>injiverify</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>injiverify</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>110</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>20-May-2026</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>injiverify</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>19-May-2026</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1457,112 +1457,112 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>22-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>928</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>928</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>19-May-2026</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1603,87 +1603,87 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>22-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>20-May-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>19-May-2026</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1749,87 +1749,87 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>22-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>20-May-2026</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>19-May-2026</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1895,87 +1895,87 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>22-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>masterdata-hin</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>masterdata-hin</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>20-May-2026</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>masterdata-hin</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>19-May-2026</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -2041,87 +2041,87 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>22-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>masterdata-kan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>masterdata-kan</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>20-May-2026</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>masterdata-kan</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>19-May-2026</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -2187,87 +2187,87 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>22-May-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>masterdata-tam</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>masterdata-tam</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>20-May-2026</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>masterdata-tam</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>19-May-2026</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -2333,87 +2333,87 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>22-May-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>mimoto</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>mimoto</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>357</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>320</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>20-May-2026</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>mimoto</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>357</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>19-May-2026</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -2479,87 +2479,87 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>22-May-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>349</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>20-May-2026</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>349</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>19-May-2026</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -2625,87 +2625,87 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>22-May-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>20-May-2026</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>19-May-2026</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
@@ -2771,87 +2771,87 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>22-May-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>1139</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
         <is>
           <t>20-May-2026</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>1054</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>19-May-2026</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -2917,87 +2917,87 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>22-May-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
         <is>
           <t>20-May-2026</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>19-May-2026</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
@@ -3063,112 +3063,112 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>22-May-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>adminui</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>adminui</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
         <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>adminui</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>19-May-2026</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>adminui</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
